--- a/output_phyto/phyto_Intermediate_seki_2010.xlsx
+++ b/output_phyto/phyto_Intermediate_seki_2010.xlsx
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_1</t>
+    <t xml:space="preserve">165-999A-2H-1,13-14.5</t>
   </si>
   <si>
     <t xml:space="preserve">10.1016/j.epsl.2010.01.037</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/phytoplankton_seki_2010.xlsx</t>
+    <t xml:space="preserve">phytoplankton_seki_2010_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">Mk37_2</t>
   </si>
   <si>
-    <t xml:space="preserve">alkenone unsaturation</t>
+    <t xml:space="preserve">published Uk37 temperature</t>
   </si>
   <si>
     <t xml:space="preserve">Garcia et al., 2006</t>
@@ -1484,217 +1484,217 @@
     <t xml:space="preserve">Size and growth rate corrections exist in paper, but no data are available, so do not include them here. Reported pCO2 uses the mean of the b-value range reported.</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_35</t>
+    <t xml:space="preserve">165-999A-2H-2,39-40.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-3H-2,33-34.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-4H-4,33-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-4H-5,136-138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-5H-3,71-73,0-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-5H-6,69-71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-6H-3,108-110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-7H-2,148-150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-8H-4,51-53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-9H-1,145-147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-10H-1,89-91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-10H-5,89-91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-10H-6,95-97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-10H-CC,31.5-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-2,6-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-3,13-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-5,22-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-6,25-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-7,29-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-12H-1,81-83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-13H-3,138-140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-13H-7,17-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-14H-2,70-72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-14H-4,52-54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-14H-6,35-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-15H-3,53-55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-15H-5,38-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-16H-1,54-56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-16H-6,15-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-16H-7,13.5-15.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-17H-1,143-145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-17H-3,26-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-17H-5,92-94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-2H-1,10-12</t>
   </si>
   <si>
     <t xml:space="preserve">The age model was derived from a combination of an astronomical age model based on orbital tuning for the time interval between 6 to 2.5 Ma (Tiedemann et al., 2007, doi:10.2973/odp.proc.sr.202.210.2007) and the combined foraminiferal and nannofossil biostratigraphy from 0 to 2.5 Ma (Shipboard Scientific Party, 2003, doi:10.2973/odp.proc.ir.202.112.2003) updated with a new nannofossil biostratigraphy for the time interval 0 to 2.5 Ma (Flores et al., 2006, doi:10.2973/odp.proc.sr.2</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Seki_2010_71</t>
+    <t xml:space="preserve">202-1241A-2H-4,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-2H-CC,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-3H-3,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-3H-6,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-4H-2,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-4H-6,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-5H-1,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-5H-3,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-5H-5,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-5H-7,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-6H-1,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-6H-3,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-6H-5,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-6H-6,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-7H-2,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-7H-4,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-7H-5,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-8H-1,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-8H-4,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-8H-7,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-9H-2,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-9H-5,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-9H-7,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-10H-2,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-10H-5,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-10H-CC,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-11H-3,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-11H-5,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-12H-1,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-12H-3,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-12H-5,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-13H-1,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-13H-4,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-13H-5,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-13H-6,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202-1241A-13H-CC,10-12</t>
   </si>
 </sst>
 </file>
@@ -1702,7 +1702,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1768,12 +1768,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1887,7 +1881,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1986,7 +1980,6 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2712,7 +2705,7 @@
       <c r="B5" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" t="s">
         <v>272</v>
       </c>
       <c r="D5" t="s">
@@ -2730,8 +2723,8 @@
       <c r="H5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.004</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2748,8 +2741,8 @@
       <c r="N5" t="n">
         <v>-24.2</v>
       </c>
-      <c r="O5" t="e">
-        <v>#N/A</v>
+      <c r="O5" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P5" t="e">
         <v>#N/A</v>
@@ -2760,8 +2753,8 @@
       <c r="R5" s="11" t="n">
         <v>27.4</v>
       </c>
-      <c r="S5" t="e">
-        <v>#N/A</v>
+      <c r="S5" t="n">
+        <v>3</v>
       </c>
       <c r="T5" t="e">
         <v>#N/A</v>
@@ -2778,29 +2771,29 @@
       <c r="X5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z5" t="e">
-        <v>#N/A</v>
+      <c r="Y5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA5" t="s">
         <v>278</v>
       </c>
-      <c r="AB5" t="e">
-        <v>#N/A</v>
+      <c r="AB5" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF5" t="e">
-        <v>#N/A</v>
+      <c r="AD5" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG5" t="e">
         <v>#N/A</v>
@@ -2822,7 +2815,7 @@
       <c r="B6" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" t="s">
         <v>272</v>
       </c>
       <c r="D6" t="s">
@@ -2840,8 +2833,8 @@
       <c r="H6" t="n">
         <v>0.25</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.004</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2858,8 +2851,8 @@
       <c r="N6" t="n">
         <v>-23.9</v>
       </c>
-      <c r="O6" t="e">
-        <v>#N/A</v>
+      <c r="O6" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P6" t="e">
         <v>#N/A</v>
@@ -2870,8 +2863,8 @@
       <c r="R6" s="11" t="n">
         <v>24.6</v>
       </c>
-      <c r="S6" t="e">
-        <v>#N/A</v>
+      <c r="S6" t="n">
+        <v>3</v>
       </c>
       <c r="T6" t="e">
         <v>#N/A</v>
@@ -2888,29 +2881,29 @@
       <c r="X6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z6" t="e">
-        <v>#N/A</v>
+      <c r="Y6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA6" t="s">
         <v>278</v>
       </c>
-      <c r="AB6" t="e">
-        <v>#N/A</v>
+      <c r="AB6" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF6" t="e">
-        <v>#N/A</v>
+      <c r="AD6" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG6" t="e">
         <v>#N/A</v>
@@ -2932,7 +2925,7 @@
       <c r="B7" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" t="s">
         <v>272</v>
       </c>
       <c r="D7" t="s">
@@ -2950,8 +2943,8 @@
       <c r="H7" t="n">
         <v>0.46</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.004</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2968,8 +2961,8 @@
       <c r="N7" t="n">
         <v>-23.4</v>
       </c>
-      <c r="O7" t="e">
-        <v>#N/A</v>
+      <c r="O7" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P7" t="e">
         <v>#N/A</v>
@@ -2980,8 +2973,8 @@
       <c r="R7" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="S7" t="e">
-        <v>#N/A</v>
+      <c r="S7" t="n">
+        <v>3</v>
       </c>
       <c r="T7" t="e">
         <v>#N/A</v>
@@ -2998,29 +2991,29 @@
       <c r="X7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z7" t="e">
-        <v>#N/A</v>
+      <c r="Y7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA7" t="s">
         <v>278</v>
       </c>
-      <c r="AB7" t="e">
-        <v>#N/A</v>
+      <c r="AB7" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF7" t="e">
-        <v>#N/A</v>
+      <c r="AD7" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG7" t="e">
         <v>#N/A</v>
@@ -3042,7 +3035,7 @@
       <c r="B8" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" t="s">
         <v>272</v>
       </c>
       <c r="D8" t="s">
@@ -3060,8 +3053,8 @@
       <c r="H8" t="n">
         <v>0.9</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.004</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -3078,8 +3071,8 @@
       <c r="N8" t="n">
         <v>-23.5</v>
       </c>
-      <c r="O8" t="e">
-        <v>#N/A</v>
+      <c r="O8" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P8" t="e">
         <v>#N/A</v>
@@ -3090,8 +3083,8 @@
       <c r="R8" s="11" t="n">
         <v>25.3</v>
       </c>
-      <c r="S8" t="e">
-        <v>#N/A</v>
+      <c r="S8" t="n">
+        <v>3</v>
       </c>
       <c r="T8" t="e">
         <v>#N/A</v>
@@ -3108,29 +3101,29 @@
       <c r="X8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z8" t="e">
-        <v>#N/A</v>
+      <c r="Y8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA8" t="s">
         <v>278</v>
       </c>
-      <c r="AB8" t="e">
-        <v>#N/A</v>
+      <c r="AB8" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF8" t="e">
-        <v>#N/A</v>
+      <c r="AD8" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG8" t="e">
         <v>#N/A</v>
@@ -3152,7 +3145,7 @@
       <c r="B9" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" t="s">
         <v>272</v>
       </c>
       <c r="D9" t="s">
@@ -3170,8 +3163,8 @@
       <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.006</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -3188,8 +3181,8 @@
       <c r="N9" t="n">
         <v>-22.6</v>
       </c>
-      <c r="O9" t="e">
-        <v>#N/A</v>
+      <c r="O9" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P9" t="e">
         <v>#N/A</v>
@@ -3200,8 +3193,8 @@
       <c r="R9" s="11" t="n">
         <v>27.4</v>
       </c>
-      <c r="S9" t="e">
-        <v>#N/A</v>
+      <c r="S9" t="n">
+        <v>3</v>
       </c>
       <c r="T9" t="e">
         <v>#N/A</v>
@@ -3218,29 +3211,29 @@
       <c r="X9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z9" t="e">
-        <v>#N/A</v>
+      <c r="Y9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA9" t="s">
         <v>278</v>
       </c>
-      <c r="AB9" t="e">
-        <v>#N/A</v>
+      <c r="AB9" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF9" t="e">
-        <v>#N/A</v>
+      <c r="AD9" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG9" t="e">
         <v>#N/A</v>
@@ -3262,7 +3255,7 @@
       <c r="B10" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" t="s">
         <v>272</v>
       </c>
       <c r="D10" t="s">
@@ -3280,8 +3273,8 @@
       <c r="H10" t="n">
         <v>1.2</v>
       </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+      <c r="I10" t="n">
+        <v>0.006</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -3298,8 +3291,8 @@
       <c r="N10" t="n">
         <v>-23.7</v>
       </c>
-      <c r="O10" t="e">
-        <v>#N/A</v>
+      <c r="O10" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P10" t="e">
         <v>#N/A</v>
@@ -3310,8 +3303,8 @@
       <c r="R10" s="11" t="n">
         <v>26.9</v>
       </c>
-      <c r="S10" t="e">
-        <v>#N/A</v>
+      <c r="S10" t="n">
+        <v>3</v>
       </c>
       <c r="T10" t="e">
         <v>#N/A</v>
@@ -3328,29 +3321,29 @@
       <c r="X10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z10" t="e">
-        <v>#N/A</v>
+      <c r="Y10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA10" t="s">
         <v>278</v>
       </c>
-      <c r="AB10" t="e">
-        <v>#N/A</v>
+      <c r="AB10" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF10" t="e">
-        <v>#N/A</v>
+      <c r="AD10" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG10" t="e">
         <v>#N/A</v>
@@ -3372,7 +3365,7 @@
       <c r="B11" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" t="s">
         <v>272</v>
       </c>
       <c r="D11" t="s">
@@ -3390,8 +3383,8 @@
       <c r="H11" t="n">
         <v>1.3</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.006</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -3408,8 +3401,8 @@
       <c r="N11" t="n">
         <v>-23.3</v>
       </c>
-      <c r="O11" t="e">
-        <v>#N/A</v>
+      <c r="O11" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P11" t="e">
         <v>#N/A</v>
@@ -3420,8 +3413,8 @@
       <c r="R11" s="11" t="n">
         <v>28.3</v>
       </c>
-      <c r="S11" t="e">
-        <v>#N/A</v>
+      <c r="S11" t="n">
+        <v>3</v>
       </c>
       <c r="T11" t="e">
         <v>#N/A</v>
@@ -3438,29 +3431,29 @@
       <c r="X11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z11" t="e">
-        <v>#N/A</v>
+      <c r="Y11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA11" t="s">
         <v>278</v>
       </c>
-      <c r="AB11" t="e">
-        <v>#N/A</v>
+      <c r="AB11" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF11" t="e">
-        <v>#N/A</v>
+      <c r="AD11" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG11" t="e">
         <v>#N/A</v>
@@ -3482,7 +3475,7 @@
       <c r="B12" t="s">
         <v>271</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" t="s">
         <v>272</v>
       </c>
       <c r="D12" t="s">
@@ -3500,8 +3493,8 @@
       <c r="H12" t="n">
         <v>1.5</v>
       </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+      <c r="I12" t="n">
+        <v>0.006</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3518,8 +3511,8 @@
       <c r="N12" t="n">
         <v>-23.4</v>
       </c>
-      <c r="O12" t="e">
-        <v>#N/A</v>
+      <c r="O12" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P12" t="e">
         <v>#N/A</v>
@@ -3530,8 +3523,8 @@
       <c r="R12" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="S12" t="e">
-        <v>#N/A</v>
+      <c r="S12" t="n">
+        <v>3</v>
       </c>
       <c r="T12" t="e">
         <v>#N/A</v>
@@ -3548,29 +3541,29 @@
       <c r="X12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z12" t="e">
-        <v>#N/A</v>
+      <c r="Y12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA12" t="s">
         <v>278</v>
       </c>
-      <c r="AB12" t="e">
-        <v>#N/A</v>
+      <c r="AB12" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF12" t="e">
-        <v>#N/A</v>
+      <c r="AD12" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG12" t="e">
         <v>#N/A</v>
@@ -3592,7 +3585,7 @@
       <c r="B13" t="s">
         <v>271</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" t="s">
         <v>272</v>
       </c>
       <c r="D13" t="s">
@@ -3610,8 +3603,8 @@
       <c r="H13" t="n">
         <v>1.75</v>
       </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+      <c r="I13" t="n">
+        <v>0.006</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3628,8 +3621,8 @@
       <c r="N13" t="n">
         <v>-23.8</v>
       </c>
-      <c r="O13" t="e">
-        <v>#N/A</v>
+      <c r="O13" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P13" t="e">
         <v>#N/A</v>
@@ -3640,8 +3633,8 @@
       <c r="R13" s="11" t="n">
         <v>27.7</v>
       </c>
-      <c r="S13" t="e">
-        <v>#N/A</v>
+      <c r="S13" t="n">
+        <v>3</v>
       </c>
       <c r="T13" t="e">
         <v>#N/A</v>
@@ -3658,29 +3651,29 @@
       <c r="X13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z13" t="e">
-        <v>#N/A</v>
+      <c r="Y13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA13" t="s">
         <v>278</v>
       </c>
-      <c r="AB13" t="e">
-        <v>#N/A</v>
+      <c r="AB13" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF13" t="e">
-        <v>#N/A</v>
+      <c r="AD13" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG13" t="e">
         <v>#N/A</v>
@@ -3702,7 +3695,7 @@
       <c r="B14" t="s">
         <v>271</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" t="s">
         <v>272</v>
       </c>
       <c r="D14" t="s">
@@ -3720,8 +3713,8 @@
       <c r="H14" t="n">
         <v>2.11</v>
       </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+      <c r="I14" t="n">
+        <v>0.006</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3738,8 +3731,8 @@
       <c r="N14" t="n">
         <v>-23.4</v>
       </c>
-      <c r="O14" t="e">
-        <v>#N/A</v>
+      <c r="O14" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P14" t="e">
         <v>#N/A</v>
@@ -3750,8 +3743,8 @@
       <c r="R14" s="11" t="n">
         <v>27.3</v>
       </c>
-      <c r="S14" t="e">
-        <v>#N/A</v>
+      <c r="S14" t="n">
+        <v>3</v>
       </c>
       <c r="T14" t="e">
         <v>#N/A</v>
@@ -3768,29 +3761,29 @@
       <c r="X14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z14" t="e">
-        <v>#N/A</v>
+      <c r="Y14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA14" t="s">
         <v>278</v>
       </c>
-      <c r="AB14" t="e">
-        <v>#N/A</v>
+      <c r="AB14" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF14" t="e">
-        <v>#N/A</v>
+      <c r="AD14" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG14" t="e">
         <v>#N/A</v>
@@ -3812,7 +3805,7 @@
       <c r="B15" t="s">
         <v>271</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" t="s">
         <v>272</v>
       </c>
       <c r="D15" t="s">
@@ -3830,8 +3823,8 @@
       <c r="H15" t="n">
         <v>2.31</v>
       </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+      <c r="I15" t="n">
+        <v>0.006</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3848,8 +3841,8 @@
       <c r="N15" t="n">
         <v>-23.4</v>
       </c>
-      <c r="O15" t="e">
-        <v>#N/A</v>
+      <c r="O15" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P15" t="e">
         <v>#N/A</v>
@@ -3860,8 +3853,8 @@
       <c r="R15" s="11" t="n">
         <v>28.4</v>
       </c>
-      <c r="S15" t="e">
-        <v>#N/A</v>
+      <c r="S15" t="n">
+        <v>3</v>
       </c>
       <c r="T15" t="e">
         <v>#N/A</v>
@@ -3878,29 +3871,29 @@
       <c r="X15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z15" t="e">
-        <v>#N/A</v>
+      <c r="Y15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA15" t="s">
         <v>278</v>
       </c>
-      <c r="AB15" t="e">
-        <v>#N/A</v>
+      <c r="AB15" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF15" t="e">
-        <v>#N/A</v>
+      <c r="AD15" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG15" t="e">
         <v>#N/A</v>
@@ -3922,7 +3915,7 @@
       <c r="B16" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" t="s">
         <v>272</v>
       </c>
       <c r="D16" t="s">
@@ -3940,8 +3933,8 @@
       <c r="H16" t="n">
         <v>2.59</v>
       </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+      <c r="I16" t="n">
+        <v>0.006</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -3958,8 +3951,8 @@
       <c r="N16" t="n">
         <v>-23.2</v>
       </c>
-      <c r="O16" t="e">
-        <v>#N/A</v>
+      <c r="O16" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P16" t="e">
         <v>#N/A</v>
@@ -3970,8 +3963,8 @@
       <c r="R16" s="11" t="n">
         <v>28.2</v>
       </c>
-      <c r="S16" t="e">
-        <v>#N/A</v>
+      <c r="S16" t="n">
+        <v>3</v>
       </c>
       <c r="T16" t="e">
         <v>#N/A</v>
@@ -3988,29 +3981,29 @@
       <c r="X16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z16" t="e">
-        <v>#N/A</v>
+      <c r="Y16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA16" t="s">
         <v>278</v>
       </c>
-      <c r="AB16" t="e">
-        <v>#N/A</v>
+      <c r="AB16" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF16" t="e">
-        <v>#N/A</v>
+      <c r="AD16" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG16" t="e">
         <v>#N/A</v>
@@ -4032,7 +4025,7 @@
       <c r="B17" t="s">
         <v>271</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" t="s">
         <v>272</v>
       </c>
       <c r="D17" t="s">
@@ -4050,8 +4043,8 @@
       <c r="H17" t="n">
         <v>2.79</v>
       </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+      <c r="I17" t="n">
+        <v>0.006</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -4068,8 +4061,8 @@
       <c r="N17" t="n">
         <v>-23.4</v>
       </c>
-      <c r="O17" t="e">
-        <v>#N/A</v>
+      <c r="O17" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P17" t="e">
         <v>#N/A</v>
@@ -4080,8 +4073,8 @@
       <c r="R17" s="11" t="n">
         <v>28.4</v>
       </c>
-      <c r="S17" t="e">
-        <v>#N/A</v>
+      <c r="S17" t="n">
+        <v>3</v>
       </c>
       <c r="T17" t="e">
         <v>#N/A</v>
@@ -4098,29 +4091,29 @@
       <c r="X17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z17" t="e">
-        <v>#N/A</v>
+      <c r="Y17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA17" t="s">
         <v>278</v>
       </c>
-      <c r="AB17" t="e">
-        <v>#N/A</v>
+      <c r="AB17" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF17" t="e">
-        <v>#N/A</v>
+      <c r="AD17" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG17" t="e">
         <v>#N/A</v>
@@ -4142,7 +4135,7 @@
       <c r="B18" t="s">
         <v>271</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" t="s">
         <v>272</v>
       </c>
       <c r="D18" t="s">
@@ -4160,8 +4153,8 @@
       <c r="H18" t="n">
         <v>2.82</v>
       </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+      <c r="I18" t="n">
+        <v>0.006</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -4178,8 +4171,8 @@
       <c r="N18" t="n">
         <v>-23.2</v>
       </c>
-      <c r="O18" t="e">
-        <v>#N/A</v>
+      <c r="O18" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P18" t="e">
         <v>#N/A</v>
@@ -4190,8 +4183,8 @@
       <c r="R18" s="11" t="n">
         <v>29.5</v>
       </c>
-      <c r="S18" t="e">
-        <v>#N/A</v>
+      <c r="S18" t="n">
+        <v>3</v>
       </c>
       <c r="T18" t="e">
         <v>#N/A</v>
@@ -4208,29 +4201,29 @@
       <c r="X18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z18" t="e">
-        <v>#N/A</v>
+      <c r="Y18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA18" t="s">
         <v>278</v>
       </c>
-      <c r="AB18" t="e">
-        <v>#N/A</v>
+      <c r="AB18" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF18" t="e">
-        <v>#N/A</v>
+      <c r="AD18" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG18" t="e">
         <v>#N/A</v>
@@ -4252,7 +4245,7 @@
       <c r="B19" t="s">
         <v>271</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" t="s">
         <v>272</v>
       </c>
       <c r="D19" t="s">
@@ -4270,8 +4263,8 @@
       <c r="H19" t="n">
         <v>2.89</v>
       </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+      <c r="I19" t="n">
+        <v>0.006</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -4288,8 +4281,8 @@
       <c r="N19" t="n">
         <v>-23.3</v>
       </c>
-      <c r="O19" t="e">
-        <v>#N/A</v>
+      <c r="O19" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P19" t="e">
         <v>#N/A</v>
@@ -4300,8 +4293,8 @@
       <c r="R19" s="11" t="n">
         <v>28.7</v>
       </c>
-      <c r="S19" t="e">
-        <v>#N/A</v>
+      <c r="S19" t="n">
+        <v>3</v>
       </c>
       <c r="T19" t="e">
         <v>#N/A</v>
@@ -4318,29 +4311,29 @@
       <c r="X19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z19" t="e">
-        <v>#N/A</v>
+      <c r="Y19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA19" t="s">
         <v>278</v>
       </c>
-      <c r="AB19" t="e">
-        <v>#N/A</v>
+      <c r="AB19" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF19" t="e">
-        <v>#N/A</v>
+      <c r="AD19" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG19" t="e">
         <v>#N/A</v>
@@ -4362,7 +4355,7 @@
       <c r="B20" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" t="s">
         <v>272</v>
       </c>
       <c r="D20" t="s">
@@ -4380,8 +4373,8 @@
       <c r="H20" t="n">
         <v>2.94</v>
       </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+      <c r="I20" t="n">
+        <v>0.006</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -4398,8 +4391,8 @@
       <c r="N20" t="n">
         <v>-23.4</v>
       </c>
-      <c r="O20" t="e">
-        <v>#N/A</v>
+      <c r="O20" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P20" t="e">
         <v>#N/A</v>
@@ -4410,8 +4403,8 @@
       <c r="R20" s="11" t="n">
         <v>28.3</v>
       </c>
-      <c r="S20" t="e">
-        <v>#N/A</v>
+      <c r="S20" t="n">
+        <v>3</v>
       </c>
       <c r="T20" t="e">
         <v>#N/A</v>
@@ -4428,29 +4421,29 @@
       <c r="X20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z20" t="e">
-        <v>#N/A</v>
+      <c r="Y20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA20" t="s">
         <v>278</v>
       </c>
-      <c r="AB20" t="e">
-        <v>#N/A</v>
+      <c r="AB20" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF20" t="e">
-        <v>#N/A</v>
+      <c r="AD20" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG20" t="e">
         <v>#N/A</v>
@@ -4472,7 +4465,7 @@
       <c r="B21" t="s">
         <v>271</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" t="s">
         <v>272</v>
       </c>
       <c r="D21" t="s">
@@ -4490,8 +4483,8 @@
       <c r="H21" t="n">
         <v>2.99</v>
       </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+      <c r="I21" t="n">
+        <v>0.006</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -4508,8 +4501,8 @@
       <c r="N21" t="n">
         <v>-23.8</v>
       </c>
-      <c r="O21" t="e">
-        <v>#N/A</v>
+      <c r="O21" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P21" t="e">
         <v>#N/A</v>
@@ -4520,8 +4513,8 @@
       <c r="R21" s="11" t="n">
         <v>28.9</v>
       </c>
-      <c r="S21" t="e">
-        <v>#N/A</v>
+      <c r="S21" t="n">
+        <v>3</v>
       </c>
       <c r="T21" t="e">
         <v>#N/A</v>
@@ -4538,29 +4531,29 @@
       <c r="X21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z21" t="e">
-        <v>#N/A</v>
+      <c r="Y21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA21" t="s">
         <v>278</v>
       </c>
-      <c r="AB21" t="e">
-        <v>#N/A</v>
+      <c r="AB21" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF21" t="e">
-        <v>#N/A</v>
+      <c r="AD21" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG21" t="e">
         <v>#N/A</v>
@@ -4582,7 +4575,7 @@
       <c r="B22" t="s">
         <v>271</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" t="s">
         <v>272</v>
       </c>
       <c r="D22" t="s">
@@ -4600,8 +4593,8 @@
       <c r="H22" t="n">
         <v>3.07</v>
       </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+      <c r="I22" t="n">
+        <v>0.015</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -4618,8 +4611,8 @@
       <c r="N22" t="n">
         <v>-23.9</v>
       </c>
-      <c r="O22" t="e">
-        <v>#N/A</v>
+      <c r="O22" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P22" t="e">
         <v>#N/A</v>
@@ -4630,8 +4623,8 @@
       <c r="R22" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="S22" t="e">
-        <v>#N/A</v>
+      <c r="S22" t="n">
+        <v>3</v>
       </c>
       <c r="T22" t="e">
         <v>#N/A</v>
@@ -4648,29 +4641,29 @@
       <c r="X22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z22" t="e">
-        <v>#N/A</v>
+      <c r="Y22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA22" t="s">
         <v>278</v>
       </c>
-      <c r="AB22" t="e">
-        <v>#N/A</v>
+      <c r="AB22" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF22" t="e">
-        <v>#N/A</v>
+      <c r="AD22" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG22" t="e">
         <v>#N/A</v>
@@ -4692,7 +4685,7 @@
       <c r="B23" t="s">
         <v>271</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" t="s">
         <v>272</v>
       </c>
       <c r="D23" t="s">
@@ -4710,8 +4703,8 @@
       <c r="H23" t="n">
         <v>3.12</v>
       </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+      <c r="I23" t="n">
+        <v>0.015</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -4728,8 +4721,8 @@
       <c r="N23" t="n">
         <v>-23.7</v>
       </c>
-      <c r="O23" t="e">
-        <v>#N/A</v>
+      <c r="O23" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P23" t="e">
         <v>#N/A</v>
@@ -4740,8 +4733,8 @@
       <c r="R23" s="11" t="n">
         <v>29.5</v>
       </c>
-      <c r="S23" t="e">
-        <v>#N/A</v>
+      <c r="S23" t="n">
+        <v>3</v>
       </c>
       <c r="T23" t="e">
         <v>#N/A</v>
@@ -4758,29 +4751,29 @@
       <c r="X23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z23" t="e">
-        <v>#N/A</v>
+      <c r="Y23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA23" t="s">
         <v>278</v>
       </c>
-      <c r="AB23" t="e">
-        <v>#N/A</v>
+      <c r="AB23" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF23" t="e">
-        <v>#N/A</v>
+      <c r="AD23" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG23" t="e">
         <v>#N/A</v>
@@ -4802,7 +4795,7 @@
       <c r="B24" t="s">
         <v>271</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" t="s">
         <v>272</v>
       </c>
       <c r="D24" t="s">
@@ -4820,8 +4813,8 @@
       <c r="H24" t="n">
         <v>3.17</v>
       </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+      <c r="I24" t="n">
+        <v>0.015</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -4838,8 +4831,8 @@
       <c r="N24" t="n">
         <v>-23.9</v>
       </c>
-      <c r="O24" t="e">
-        <v>#N/A</v>
+      <c r="O24" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P24" t="e">
         <v>#N/A</v>
@@ -4850,8 +4843,8 @@
       <c r="R24" s="11" t="n">
         <v>28.5</v>
       </c>
-      <c r="S24" t="e">
-        <v>#N/A</v>
+      <c r="S24" t="n">
+        <v>3</v>
       </c>
       <c r="T24" t="e">
         <v>#N/A</v>
@@ -4868,29 +4861,29 @@
       <c r="X24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z24" t="e">
-        <v>#N/A</v>
+      <c r="Y24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA24" t="s">
         <v>278</v>
       </c>
-      <c r="AB24" t="e">
-        <v>#N/A</v>
+      <c r="AB24" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF24" t="e">
-        <v>#N/A</v>
+      <c r="AD24" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG24" t="e">
         <v>#N/A</v>
@@ -4912,7 +4905,7 @@
       <c r="B25" t="s">
         <v>271</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" t="s">
         <v>272</v>
       </c>
       <c r="D25" t="s">
@@ -4930,8 +4923,8 @@
       <c r="H25" t="n">
         <v>3.23</v>
       </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+      <c r="I25" t="n">
+        <v>0.015</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -4948,8 +4941,8 @@
       <c r="N25" t="n">
         <v>-23.6</v>
       </c>
-      <c r="O25" t="e">
-        <v>#N/A</v>
+      <c r="O25" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P25" t="e">
         <v>#N/A</v>
@@ -4960,8 +4953,8 @@
       <c r="R25" s="11" t="n">
         <v>28.4</v>
       </c>
-      <c r="S25" t="e">
-        <v>#N/A</v>
+      <c r="S25" t="n">
+        <v>3</v>
       </c>
       <c r="T25" t="e">
         <v>#N/A</v>
@@ -4978,29 +4971,29 @@
       <c r="X25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z25" t="e">
-        <v>#N/A</v>
+      <c r="Y25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA25" t="s">
         <v>278</v>
       </c>
-      <c r="AB25" t="e">
-        <v>#N/A</v>
+      <c r="AB25" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF25" t="e">
-        <v>#N/A</v>
+      <c r="AD25" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG25" t="e">
         <v>#N/A</v>
@@ -5022,7 +5015,7 @@
       <c r="B26" t="s">
         <v>271</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" t="s">
         <v>272</v>
       </c>
       <c r="D26" t="s">
@@ -5040,8 +5033,8 @@
       <c r="H26" t="n">
         <v>3.62</v>
       </c>
-      <c r="I26" t="e">
-        <v>#N/A</v>
+      <c r="I26" t="n">
+        <v>0.015</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -5058,8 +5051,8 @@
       <c r="N26" t="n">
         <v>-23.8</v>
       </c>
-      <c r="O26" t="e">
-        <v>#N/A</v>
+      <c r="O26" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P26" t="e">
         <v>#N/A</v>
@@ -5070,8 +5063,8 @@
       <c r="R26" s="11" t="n">
         <v>28.9</v>
       </c>
-      <c r="S26" t="e">
-        <v>#N/A</v>
+      <c r="S26" t="n">
+        <v>3</v>
       </c>
       <c r="T26" t="e">
         <v>#N/A</v>
@@ -5088,29 +5081,29 @@
       <c r="X26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z26" t="e">
-        <v>#N/A</v>
+      <c r="Y26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA26" t="s">
         <v>278</v>
       </c>
-      <c r="AB26" t="e">
-        <v>#N/A</v>
+      <c r="AB26" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF26" t="e">
-        <v>#N/A</v>
+      <c r="AD26" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG26" t="e">
         <v>#N/A</v>
@@ -5132,7 +5125,7 @@
       <c r="B27" t="s">
         <v>271</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="C27" t="s">
         <v>272</v>
       </c>
       <c r="D27" t="s">
@@ -5150,8 +5143,8 @@
       <c r="H27" t="n">
         <v>3.85</v>
       </c>
-      <c r="I27" t="e">
-        <v>#N/A</v>
+      <c r="I27" t="n">
+        <v>0.015</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -5168,8 +5161,8 @@
       <c r="N27" t="n">
         <v>-24.2</v>
       </c>
-      <c r="O27" t="e">
-        <v>#N/A</v>
+      <c r="O27" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P27" t="e">
         <v>#N/A</v>
@@ -5180,8 +5173,8 @@
       <c r="R27" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="S27" t="e">
-        <v>#N/A</v>
+      <c r="S27" t="n">
+        <v>3</v>
       </c>
       <c r="T27" t="e">
         <v>#N/A</v>
@@ -5198,29 +5191,29 @@
       <c r="X27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z27" t="e">
-        <v>#N/A</v>
+      <c r="Y27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA27" t="s">
         <v>278</v>
       </c>
-      <c r="AB27" t="e">
-        <v>#N/A</v>
+      <c r="AB27" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF27" t="e">
-        <v>#N/A</v>
+      <c r="AD27" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG27" t="e">
         <v>#N/A</v>
@@ -5242,7 +5235,7 @@
       <c r="B28" t="s">
         <v>271</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" t="s">
         <v>272</v>
       </c>
       <c r="D28" t="s">
@@ -5260,8 +5253,8 @@
       <c r="H28" t="n">
         <v>3.93</v>
       </c>
-      <c r="I28" t="e">
-        <v>#N/A</v>
+      <c r="I28" t="n">
+        <v>0.015</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -5278,8 +5271,8 @@
       <c r="N28" t="n">
         <v>-23.9</v>
       </c>
-      <c r="O28" t="e">
-        <v>#N/A</v>
+      <c r="O28" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P28" t="e">
         <v>#N/A</v>
@@ -5290,8 +5283,8 @@
       <c r="R28" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="S28" t="e">
-        <v>#N/A</v>
+      <c r="S28" t="n">
+        <v>3</v>
       </c>
       <c r="T28" t="e">
         <v>#N/A</v>
@@ -5308,29 +5301,29 @@
       <c r="X28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z28" t="e">
-        <v>#N/A</v>
+      <c r="Y28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA28" t="s">
         <v>278</v>
       </c>
-      <c r="AB28" t="e">
-        <v>#N/A</v>
+      <c r="AB28" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF28" t="e">
-        <v>#N/A</v>
+      <c r="AD28" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG28" t="e">
         <v>#N/A</v>
@@ -5352,7 +5345,7 @@
       <c r="B29" t="s">
         <v>271</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" t="s">
         <v>272</v>
       </c>
       <c r="D29" t="s">
@@ -5370,8 +5363,8 @@
       <c r="H29" t="n">
         <v>4.03</v>
       </c>
-      <c r="I29" t="e">
-        <v>#N/A</v>
+      <c r="I29" t="n">
+        <v>0.03</v>
       </c>
       <c r="J29" t="e">
         <v>#N/A</v>
@@ -5388,8 +5381,8 @@
       <c r="N29" t="n">
         <v>-23.5</v>
       </c>
-      <c r="O29" t="e">
-        <v>#N/A</v>
+      <c r="O29" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P29" t="e">
         <v>#N/A</v>
@@ -5400,8 +5393,8 @@
       <c r="R29" s="11" t="n">
         <v>29.8</v>
       </c>
-      <c r="S29" t="e">
-        <v>#N/A</v>
+      <c r="S29" t="n">
+        <v>3</v>
       </c>
       <c r="T29" t="e">
         <v>#N/A</v>
@@ -5418,29 +5411,29 @@
       <c r="X29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z29" t="e">
-        <v>#N/A</v>
+      <c r="Y29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA29" t="s">
         <v>278</v>
       </c>
-      <c r="AB29" t="e">
-        <v>#N/A</v>
+      <c r="AB29" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF29" t="e">
-        <v>#N/A</v>
+      <c r="AD29" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG29" t="e">
         <v>#N/A</v>
@@ -5462,7 +5455,7 @@
       <c r="B30" t="s">
         <v>271</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C30" t="s">
         <v>272</v>
       </c>
       <c r="D30" t="s">
@@ -5480,8 +5473,8 @@
       <c r="H30" t="n">
         <v>4.11</v>
       </c>
-      <c r="I30" t="e">
-        <v>#N/A</v>
+      <c r="I30" t="n">
+        <v>0.03</v>
       </c>
       <c r="J30" t="e">
         <v>#N/A</v>
@@ -5498,8 +5491,8 @@
       <c r="N30" t="n">
         <v>-24.1</v>
       </c>
-      <c r="O30" t="e">
-        <v>#N/A</v>
+      <c r="O30" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P30" t="e">
         <v>#N/A</v>
@@ -5510,8 +5503,8 @@
       <c r="R30" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="S30" t="e">
-        <v>#N/A</v>
+      <c r="S30" t="n">
+        <v>3</v>
       </c>
       <c r="T30" t="e">
         <v>#N/A</v>
@@ -5528,29 +5521,29 @@
       <c r="X30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z30" t="e">
-        <v>#N/A</v>
+      <c r="Y30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA30" t="s">
         <v>278</v>
       </c>
-      <c r="AB30" t="e">
-        <v>#N/A</v>
+      <c r="AB30" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF30" t="e">
-        <v>#N/A</v>
+      <c r="AD30" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG30" t="e">
         <v>#N/A</v>
@@ -5572,7 +5565,7 @@
       <c r="B31" t="s">
         <v>271</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" t="s">
         <v>272</v>
       </c>
       <c r="D31" t="s">
@@ -5590,8 +5583,8 @@
       <c r="H31" t="n">
         <v>4.34</v>
       </c>
-      <c r="I31" t="e">
-        <v>#N/A</v>
+      <c r="I31" t="n">
+        <v>0.03</v>
       </c>
       <c r="J31" t="e">
         <v>#N/A</v>
@@ -5608,8 +5601,8 @@
       <c r="N31" t="n">
         <v>-24.1</v>
       </c>
-      <c r="O31" t="e">
-        <v>#N/A</v>
+      <c r="O31" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P31" t="e">
         <v>#N/A</v>
@@ -5620,8 +5613,8 @@
       <c r="R31" s="11" t="n">
         <v>30.1</v>
       </c>
-      <c r="S31" t="e">
-        <v>#N/A</v>
+      <c r="S31" t="n">
+        <v>3</v>
       </c>
       <c r="T31" t="e">
         <v>#N/A</v>
@@ -5638,29 +5631,29 @@
       <c r="X31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z31" t="e">
-        <v>#N/A</v>
+      <c r="Y31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA31" t="s">
         <v>278</v>
       </c>
-      <c r="AB31" t="e">
-        <v>#N/A</v>
+      <c r="AB31" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF31" t="e">
-        <v>#N/A</v>
+      <c r="AD31" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG31" t="e">
         <v>#N/A</v>
@@ -5682,7 +5675,7 @@
       <c r="B32" t="s">
         <v>271</v>
       </c>
-      <c r="C32" s="34" t="s">
+      <c r="C32" t="s">
         <v>272</v>
       </c>
       <c r="D32" t="s">
@@ -5700,8 +5693,8 @@
       <c r="H32" t="n">
         <v>4.43</v>
       </c>
-      <c r="I32" t="e">
-        <v>#N/A</v>
+      <c r="I32" t="n">
+        <v>0.03</v>
       </c>
       <c r="J32" t="e">
         <v>#N/A</v>
@@ -5718,8 +5711,8 @@
       <c r="N32" t="n">
         <v>-23.6</v>
       </c>
-      <c r="O32" t="e">
-        <v>#N/A</v>
+      <c r="O32" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P32" t="e">
         <v>#N/A</v>
@@ -5730,8 +5723,8 @@
       <c r="R32" s="11" t="n">
         <v>29.4</v>
       </c>
-      <c r="S32" t="e">
-        <v>#N/A</v>
+      <c r="S32" t="n">
+        <v>3</v>
       </c>
       <c r="T32" t="e">
         <v>#N/A</v>
@@ -5748,29 +5741,29 @@
       <c r="X32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z32" t="e">
-        <v>#N/A</v>
+      <c r="Y32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA32" t="s">
         <v>278</v>
       </c>
-      <c r="AB32" t="e">
-        <v>#N/A</v>
+      <c r="AB32" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF32" t="e">
-        <v>#N/A</v>
+      <c r="AD32" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG32" t="e">
         <v>#N/A</v>
@@ -5792,7 +5785,7 @@
       <c r="B33" t="s">
         <v>271</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" t="s">
         <v>272</v>
       </c>
       <c r="D33" t="s">
@@ -5810,8 +5803,8 @@
       <c r="H33" t="n">
         <v>4.58</v>
       </c>
-      <c r="I33" t="e">
-        <v>#N/A</v>
+      <c r="I33" t="n">
+        <v>0.03</v>
       </c>
       <c r="J33" t="e">
         <v>#N/A</v>
@@ -5828,8 +5821,8 @@
       <c r="N33" t="n">
         <v>-24.2</v>
       </c>
-      <c r="O33" t="e">
-        <v>#N/A</v>
+      <c r="O33" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P33" t="e">
         <v>#N/A</v>
@@ -5840,8 +5833,8 @@
       <c r="R33" s="11" t="n">
         <v>29.5</v>
       </c>
-      <c r="S33" t="e">
-        <v>#N/A</v>
+      <c r="S33" t="n">
+        <v>3</v>
       </c>
       <c r="T33" t="e">
         <v>#N/A</v>
@@ -5858,29 +5851,29 @@
       <c r="X33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z33" t="e">
-        <v>#N/A</v>
+      <c r="Y33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA33" t="s">
         <v>278</v>
       </c>
-      <c r="AB33" t="e">
-        <v>#N/A</v>
+      <c r="AB33" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF33" t="e">
-        <v>#N/A</v>
+      <c r="AD33" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG33" t="e">
         <v>#N/A</v>
@@ -5902,7 +5895,7 @@
       <c r="B34" t="s">
         <v>271</v>
       </c>
-      <c r="C34" s="34" t="s">
+      <c r="C34" t="s">
         <v>272</v>
       </c>
       <c r="D34" t="s">
@@ -5920,8 +5913,8 @@
       <c r="H34" t="n">
         <v>4.78</v>
       </c>
-      <c r="I34" t="e">
-        <v>#N/A</v>
+      <c r="I34" t="n">
+        <v>0.03</v>
       </c>
       <c r="J34" t="e">
         <v>#N/A</v>
@@ -5938,8 +5931,8 @@
       <c r="N34" t="n">
         <v>-23.9</v>
       </c>
-      <c r="O34" t="e">
-        <v>#N/A</v>
+      <c r="O34" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P34" t="e">
         <v>#N/A</v>
@@ -5950,8 +5943,8 @@
       <c r="R34" s="11" t="n">
         <v>28.9</v>
       </c>
-      <c r="S34" t="e">
-        <v>#N/A</v>
+      <c r="S34" t="n">
+        <v>3</v>
       </c>
       <c r="T34" t="e">
         <v>#N/A</v>
@@ -5968,29 +5961,29 @@
       <c r="X34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z34" t="e">
-        <v>#N/A</v>
+      <c r="Y34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA34" t="s">
         <v>278</v>
       </c>
-      <c r="AB34" t="e">
-        <v>#N/A</v>
+      <c r="AB34" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF34" t="e">
-        <v>#N/A</v>
+      <c r="AD34" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG34" t="e">
         <v>#N/A</v>
@@ -6012,7 +6005,7 @@
       <c r="B35" t="s">
         <v>271</v>
       </c>
-      <c r="C35" s="34" t="s">
+      <c r="C35" t="s">
         <v>272</v>
       </c>
       <c r="D35" t="s">
@@ -6030,8 +6023,8 @@
       <c r="H35" t="n">
         <v>4.86</v>
       </c>
-      <c r="I35" t="e">
-        <v>#N/A</v>
+      <c r="I35" t="n">
+        <v>0.03</v>
       </c>
       <c r="J35" t="e">
         <v>#N/A</v>
@@ -6048,8 +6041,8 @@
       <c r="N35" t="n">
         <v>-23.4</v>
       </c>
-      <c r="O35" t="e">
-        <v>#N/A</v>
+      <c r="O35" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P35" t="e">
         <v>#N/A</v>
@@ -6060,8 +6053,8 @@
       <c r="R35" s="11" t="n">
         <v>28.8</v>
       </c>
-      <c r="S35" t="e">
-        <v>#N/A</v>
+      <c r="S35" t="n">
+        <v>3</v>
       </c>
       <c r="T35" t="e">
         <v>#N/A</v>
@@ -6078,29 +6071,29 @@
       <c r="X35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z35" t="e">
-        <v>#N/A</v>
+      <c r="Y35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA35" t="s">
         <v>278</v>
       </c>
-      <c r="AB35" t="e">
-        <v>#N/A</v>
+      <c r="AB35" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF35" t="e">
-        <v>#N/A</v>
+      <c r="AD35" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG35" t="e">
         <v>#N/A</v>
@@ -6122,7 +6115,7 @@
       <c r="B36" t="s">
         <v>271</v>
       </c>
-      <c r="C36" s="34" t="s">
+      <c r="C36" t="s">
         <v>272</v>
       </c>
       <c r="D36" t="s">
@@ -6140,8 +6133,8 @@
       <c r="H36" t="n">
         <v>4.94</v>
       </c>
-      <c r="I36" t="e">
-        <v>#N/A</v>
+      <c r="I36" t="n">
+        <v>0.03</v>
       </c>
       <c r="J36" t="e">
         <v>#N/A</v>
@@ -6158,8 +6151,8 @@
       <c r="N36" t="n">
         <v>-23.3</v>
       </c>
-      <c r="O36" t="e">
-        <v>#N/A</v>
+      <c r="O36" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P36" t="e">
         <v>#N/A</v>
@@ -6170,8 +6163,8 @@
       <c r="R36" s="11" t="n">
         <v>28.9</v>
       </c>
-      <c r="S36" t="e">
-        <v>#N/A</v>
+      <c r="S36" t="n">
+        <v>3</v>
       </c>
       <c r="T36" t="e">
         <v>#N/A</v>
@@ -6188,29 +6181,29 @@
       <c r="X36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z36" t="e">
-        <v>#N/A</v>
+      <c r="Y36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA36" t="s">
         <v>278</v>
       </c>
-      <c r="AB36" t="e">
-        <v>#N/A</v>
+      <c r="AB36" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF36" t="e">
-        <v>#N/A</v>
+      <c r="AD36" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG36" t="e">
         <v>#N/A</v>
@@ -6232,7 +6225,7 @@
       <c r="B37" t="s">
         <v>271</v>
       </c>
-      <c r="C37" s="34" t="s">
+      <c r="C37" t="s">
         <v>272</v>
       </c>
       <c r="D37" t="s">
@@ -6250,8 +6243,8 @@
       <c r="H37" t="n">
         <v>5.04</v>
       </c>
-      <c r="I37" t="e">
-        <v>#N/A</v>
+      <c r="I37" t="n">
+        <v>0.04</v>
       </c>
       <c r="J37" t="e">
         <v>#N/A</v>
@@ -6268,8 +6261,8 @@
       <c r="N37" t="n">
         <v>-23.5</v>
       </c>
-      <c r="O37" t="e">
-        <v>#N/A</v>
+      <c r="O37" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P37" t="e">
         <v>#N/A</v>
@@ -6280,8 +6273,8 @@
       <c r="R37" s="11" t="n">
         <v>29.4</v>
       </c>
-      <c r="S37" t="e">
-        <v>#N/A</v>
+      <c r="S37" t="n">
+        <v>3</v>
       </c>
       <c r="T37" t="e">
         <v>#N/A</v>
@@ -6298,29 +6291,29 @@
       <c r="X37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z37" t="e">
-        <v>#N/A</v>
+      <c r="Y37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA37" t="s">
         <v>278</v>
       </c>
-      <c r="AB37" t="e">
-        <v>#N/A</v>
+      <c r="AB37" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF37" t="e">
-        <v>#N/A</v>
+      <c r="AD37" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG37" t="e">
         <v>#N/A</v>
@@ -6342,7 +6335,7 @@
       <c r="B38" t="s">
         <v>271</v>
       </c>
-      <c r="C38" s="34" t="s">
+      <c r="C38" t="s">
         <v>272</v>
       </c>
       <c r="D38" t="s">
@@ -6360,8 +6353,8 @@
       <c r="H38" t="n">
         <v>5.19</v>
       </c>
-      <c r="I38" t="e">
-        <v>#N/A</v>
+      <c r="I38" t="n">
+        <v>0.04</v>
       </c>
       <c r="J38" t="e">
         <v>#N/A</v>
@@ -6378,8 +6371,8 @@
       <c r="N38" t="n">
         <v>-23.7</v>
       </c>
-      <c r="O38" t="e">
-        <v>#N/A</v>
+      <c r="O38" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P38" t="e">
         <v>#N/A</v>
@@ -6390,8 +6383,8 @@
       <c r="R38" s="11" t="n">
         <v>29.9</v>
       </c>
-      <c r="S38" t="e">
-        <v>#N/A</v>
+      <c r="S38" t="n">
+        <v>3</v>
       </c>
       <c r="T38" t="e">
         <v>#N/A</v>
@@ -6408,29 +6401,29 @@
       <c r="X38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z38" t="e">
-        <v>#N/A</v>
+      <c r="Y38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.15</v>
       </c>
       <c r="AA38" t="s">
         <v>278</v>
       </c>
-      <c r="AB38" t="e">
-        <v>#N/A</v>
+      <c r="AB38" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF38" t="e">
-        <v>#N/A</v>
+      <c r="AD38" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG38" t="e">
         <v>#N/A</v>
@@ -6452,7 +6445,7 @@
       <c r="B39" t="s">
         <v>271</v>
       </c>
-      <c r="C39" s="34" t="s">
+      <c r="C39" t="s">
         <v>272</v>
       </c>
       <c r="D39" t="s">
@@ -6470,8 +6463,8 @@
       <c r="H39" t="n">
         <v>0.21</v>
       </c>
-      <c r="I39" t="e">
-        <v>#N/A</v>
+      <c r="I39" t="n">
+        <v>0.004</v>
       </c>
       <c r="J39" t="e">
         <v>#N/A</v>
@@ -6488,8 +6481,8 @@
       <c r="N39" t="n">
         <v>-24.3</v>
       </c>
-      <c r="O39" t="e">
-        <v>#N/A</v>
+      <c r="O39" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P39" t="e">
         <v>#N/A</v>
@@ -6500,8 +6493,8 @@
       <c r="R39" s="11" t="n">
         <v>27.4</v>
       </c>
-      <c r="S39" t="e">
-        <v>#N/A</v>
+      <c r="S39" t="n">
+        <v>3</v>
       </c>
       <c r="T39" t="e">
         <v>#N/A</v>
@@ -6518,29 +6511,29 @@
       <c r="X39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z39" t="e">
-        <v>#N/A</v>
+      <c r="Y39" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA39" t="s">
         <v>278</v>
       </c>
-      <c r="AB39" t="e">
-        <v>#N/A</v>
+      <c r="AB39" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF39" t="e">
-        <v>#N/A</v>
+      <c r="AD39" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG39" t="e">
         <v>#N/A</v>
@@ -6562,7 +6555,7 @@
       <c r="B40" t="s">
         <v>271</v>
       </c>
-      <c r="C40" s="34" t="s">
+      <c r="C40" t="s">
         <v>272</v>
       </c>
       <c r="D40" t="s">
@@ -6580,8 +6573,8 @@
       <c r="H40" t="n">
         <v>0.45</v>
       </c>
-      <c r="I40" t="e">
-        <v>#N/A</v>
+      <c r="I40" t="n">
+        <v>0.004</v>
       </c>
       <c r="J40" t="e">
         <v>#N/A</v>
@@ -6598,8 +6591,8 @@
       <c r="N40" t="n">
         <v>-24.1</v>
       </c>
-      <c r="O40" t="e">
-        <v>#N/A</v>
+      <c r="O40" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P40" t="e">
         <v>#N/A</v>
@@ -6610,8 +6603,8 @@
       <c r="R40" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="S40" t="e">
-        <v>#N/A</v>
+      <c r="S40" t="n">
+        <v>3</v>
       </c>
       <c r="T40" t="e">
         <v>#N/A</v>
@@ -6628,29 +6621,29 @@
       <c r="X40" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z40" t="e">
-        <v>#N/A</v>
+      <c r="Y40" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA40" t="s">
         <v>278</v>
       </c>
-      <c r="AB40" t="e">
-        <v>#N/A</v>
+      <c r="AB40" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC40" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF40" t="e">
-        <v>#N/A</v>
+      <c r="AD40" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG40" t="e">
         <v>#N/A</v>
@@ -6672,7 +6665,7 @@
       <c r="B41" t="s">
         <v>271</v>
       </c>
-      <c r="C41" s="34" t="s">
+      <c r="C41" t="s">
         <v>272</v>
       </c>
       <c r="D41" t="s">
@@ -6690,8 +6683,8 @@
       <c r="H41" t="n">
         <v>0.68</v>
       </c>
-      <c r="I41" t="e">
-        <v>#N/A</v>
+      <c r="I41" t="n">
+        <v>0.004</v>
       </c>
       <c r="J41" t="e">
         <v>#N/A</v>
@@ -6708,8 +6701,8 @@
       <c r="N41" t="n">
         <v>-23.5</v>
       </c>
-      <c r="O41" t="e">
-        <v>#N/A</v>
+      <c r="O41" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P41" t="e">
         <v>#N/A</v>
@@ -6720,8 +6713,8 @@
       <c r="R41" s="11" t="n">
         <v>28.1</v>
       </c>
-      <c r="S41" t="e">
-        <v>#N/A</v>
+      <c r="S41" t="n">
+        <v>3</v>
       </c>
       <c r="T41" t="e">
         <v>#N/A</v>
@@ -6738,29 +6731,29 @@
       <c r="X41" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z41" t="e">
-        <v>#N/A</v>
+      <c r="Y41" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA41" t="s">
         <v>278</v>
       </c>
-      <c r="AB41" t="e">
-        <v>#N/A</v>
+      <c r="AB41" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC41" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF41" t="e">
-        <v>#N/A</v>
+      <c r="AD41" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG41" t="e">
         <v>#N/A</v>
@@ -6782,7 +6775,7 @@
       <c r="B42" t="s">
         <v>271</v>
       </c>
-      <c r="C42" s="34" t="s">
+      <c r="C42" t="s">
         <v>272</v>
       </c>
       <c r="D42" t="s">
@@ -6800,8 +6793,8 @@
       <c r="H42" t="n">
         <v>0.82</v>
       </c>
-      <c r="I42" t="e">
-        <v>#N/A</v>
+      <c r="I42" t="n">
+        <v>0.004</v>
       </c>
       <c r="J42" t="e">
         <v>#N/A</v>
@@ -6818,8 +6811,8 @@
       <c r="N42" t="n">
         <v>-24</v>
       </c>
-      <c r="O42" t="e">
-        <v>#N/A</v>
+      <c r="O42" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P42" t="e">
         <v>#N/A</v>
@@ -6830,8 +6823,8 @@
       <c r="R42" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="S42" t="e">
-        <v>#N/A</v>
+      <c r="S42" t="n">
+        <v>3</v>
       </c>
       <c r="T42" t="e">
         <v>#N/A</v>
@@ -6848,29 +6841,29 @@
       <c r="X42" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z42" t="e">
-        <v>#N/A</v>
+      <c r="Y42" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA42" t="s">
         <v>278</v>
       </c>
-      <c r="AB42" t="e">
-        <v>#N/A</v>
+      <c r="AB42" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC42" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF42" t="e">
-        <v>#N/A</v>
+      <c r="AD42" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG42" t="e">
         <v>#N/A</v>
@@ -6892,7 +6885,7 @@
       <c r="B43" t="s">
         <v>271</v>
       </c>
-      <c r="C43" s="34" t="s">
+      <c r="C43" t="s">
         <v>272</v>
       </c>
       <c r="D43" t="s">
@@ -6910,8 +6903,8 @@
       <c r="H43" t="n">
         <v>1.08</v>
       </c>
-      <c r="I43" t="e">
-        <v>#N/A</v>
+      <c r="I43" t="n">
+        <v>0.006</v>
       </c>
       <c r="J43" t="e">
         <v>#N/A</v>
@@ -6928,8 +6921,8 @@
       <c r="N43" t="n">
         <v>-23.9</v>
       </c>
-      <c r="O43" t="e">
-        <v>#N/A</v>
+      <c r="O43" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P43" t="e">
         <v>#N/A</v>
@@ -6940,8 +6933,8 @@
       <c r="R43" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="S43" t="e">
-        <v>#N/A</v>
+      <c r="S43" t="n">
+        <v>3</v>
       </c>
       <c r="T43" t="e">
         <v>#N/A</v>
@@ -6958,29 +6951,29 @@
       <c r="X43" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z43" t="e">
-        <v>#N/A</v>
+      <c r="Y43" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA43" t="s">
         <v>278</v>
       </c>
-      <c r="AB43" t="e">
-        <v>#N/A</v>
+      <c r="AB43" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC43" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF43" t="e">
-        <v>#N/A</v>
+      <c r="AD43" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG43" t="e">
         <v>#N/A</v>
@@ -7002,7 +6995,7 @@
       <c r="B44" t="s">
         <v>271</v>
       </c>
-      <c r="C44" s="34" t="s">
+      <c r="C44" t="s">
         <v>272</v>
       </c>
       <c r="D44" t="s">
@@ -7020,8 +7013,8 @@
       <c r="H44" t="n">
         <v>1.25</v>
       </c>
-      <c r="I44" t="e">
-        <v>#N/A</v>
+      <c r="I44" t="n">
+        <v>0.006</v>
       </c>
       <c r="J44" t="e">
         <v>#N/A</v>
@@ -7038,8 +7031,8 @@
       <c r="N44" t="n">
         <v>-23.9</v>
       </c>
-      <c r="O44" t="e">
-        <v>#N/A</v>
+      <c r="O44" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P44" t="e">
         <v>#N/A</v>
@@ -7050,8 +7043,8 @@
       <c r="R44" s="11" t="n">
         <v>28.1</v>
       </c>
-      <c r="S44" t="e">
-        <v>#N/A</v>
+      <c r="S44" t="n">
+        <v>3</v>
       </c>
       <c r="T44" t="e">
         <v>#N/A</v>
@@ -7068,29 +7061,29 @@
       <c r="X44" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z44" t="e">
-        <v>#N/A</v>
+      <c r="Y44" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA44" t="s">
         <v>278</v>
       </c>
-      <c r="AB44" t="e">
-        <v>#N/A</v>
+      <c r="AB44" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC44" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF44" t="e">
-        <v>#N/A</v>
+      <c r="AD44" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG44" t="e">
         <v>#N/A</v>
@@ -7112,7 +7105,7 @@
       <c r="B45" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="34" t="s">
+      <c r="C45" t="s">
         <v>272</v>
       </c>
       <c r="D45" t="s">
@@ -7130,8 +7123,8 @@
       <c r="H45" t="n">
         <v>1.56</v>
       </c>
-      <c r="I45" t="e">
-        <v>#N/A</v>
+      <c r="I45" t="n">
+        <v>0.006</v>
       </c>
       <c r="J45" t="e">
         <v>#N/A</v>
@@ -7148,8 +7141,8 @@
       <c r="N45" t="n">
         <v>-23.2</v>
       </c>
-      <c r="O45" t="e">
-        <v>#N/A</v>
+      <c r="O45" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P45" t="e">
         <v>#N/A</v>
@@ -7160,8 +7153,8 @@
       <c r="R45" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="S45" t="e">
-        <v>#N/A</v>
+      <c r="S45" t="n">
+        <v>3</v>
       </c>
       <c r="T45" t="e">
         <v>#N/A</v>
@@ -7178,29 +7171,29 @@
       <c r="X45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z45" t="e">
-        <v>#N/A</v>
+      <c r="Y45" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA45" t="s">
         <v>278</v>
       </c>
-      <c r="AB45" t="e">
-        <v>#N/A</v>
+      <c r="AB45" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF45" t="e">
-        <v>#N/A</v>
+      <c r="AD45" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG45" t="e">
         <v>#N/A</v>
@@ -7222,7 +7215,7 @@
       <c r="B46" t="s">
         <v>271</v>
       </c>
-      <c r="C46" s="34" t="s">
+      <c r="C46" t="s">
         <v>272</v>
       </c>
       <c r="D46" t="s">
@@ -7240,8 +7233,8 @@
       <c r="H46" t="n">
         <v>1.6</v>
       </c>
-      <c r="I46" t="e">
-        <v>#N/A</v>
+      <c r="I46" t="n">
+        <v>0.006</v>
       </c>
       <c r="J46" t="e">
         <v>#N/A</v>
@@ -7258,8 +7251,8 @@
       <c r="N46" t="n">
         <v>-23.4</v>
       </c>
-      <c r="O46" t="e">
-        <v>#N/A</v>
+      <c r="O46" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P46" t="e">
         <v>#N/A</v>
@@ -7270,8 +7263,8 @@
       <c r="R46" s="11" t="n">
         <v>28.4</v>
       </c>
-      <c r="S46" t="e">
-        <v>#N/A</v>
+      <c r="S46" t="n">
+        <v>3</v>
       </c>
       <c r="T46" t="e">
         <v>#N/A</v>
@@ -7288,29 +7281,29 @@
       <c r="X46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z46" t="e">
-        <v>#N/A</v>
+      <c r="Y46" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA46" t="s">
         <v>278</v>
       </c>
-      <c r="AB46" t="e">
-        <v>#N/A</v>
+      <c r="AB46" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF46" t="e">
-        <v>#N/A</v>
+      <c r="AD46" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG46" t="e">
         <v>#N/A</v>
@@ -7332,7 +7325,7 @@
       <c r="B47" t="s">
         <v>271</v>
       </c>
-      <c r="C47" s="34" t="s">
+      <c r="C47" t="s">
         <v>272</v>
       </c>
       <c r="D47" t="s">
@@ -7350,8 +7343,8 @@
       <c r="H47" t="n">
         <v>1.72</v>
       </c>
-      <c r="I47" t="e">
-        <v>#N/A</v>
+      <c r="I47" t="n">
+        <v>0.006</v>
       </c>
       <c r="J47" t="e">
         <v>#N/A</v>
@@ -7368,8 +7361,8 @@
       <c r="N47" t="n">
         <v>-23.6</v>
       </c>
-      <c r="O47" t="e">
-        <v>#N/A</v>
+      <c r="O47" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P47" t="e">
         <v>#N/A</v>
@@ -7380,8 +7373,8 @@
       <c r="R47" s="11" t="n">
         <v>27.3</v>
       </c>
-      <c r="S47" t="e">
-        <v>#N/A</v>
+      <c r="S47" t="n">
+        <v>3</v>
       </c>
       <c r="T47" t="e">
         <v>#N/A</v>
@@ -7398,29 +7391,29 @@
       <c r="X47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z47" t="e">
-        <v>#N/A</v>
+      <c r="Y47" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA47" t="s">
         <v>278</v>
       </c>
-      <c r="AB47" t="e">
-        <v>#N/A</v>
+      <c r="AB47" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF47" t="e">
-        <v>#N/A</v>
+      <c r="AD47" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG47" t="e">
         <v>#N/A</v>
@@ -7442,7 +7435,7 @@
       <c r="B48" t="s">
         <v>271</v>
       </c>
-      <c r="C48" s="34" t="s">
+      <c r="C48" t="s">
         <v>272</v>
       </c>
       <c r="D48" t="s">
@@ -7460,8 +7453,8 @@
       <c r="H48" t="n">
         <v>1.83</v>
       </c>
-      <c r="I48" t="e">
-        <v>#N/A</v>
+      <c r="I48" t="n">
+        <v>0.006</v>
       </c>
       <c r="J48" t="e">
         <v>#N/A</v>
@@ -7478,8 +7471,8 @@
       <c r="N48" t="n">
         <v>-23.6</v>
       </c>
-      <c r="O48" t="e">
-        <v>#N/A</v>
+      <c r="O48" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P48" t="e">
         <v>#N/A</v>
@@ -7490,8 +7483,8 @@
       <c r="R48" s="11" t="n">
         <v>27.9</v>
       </c>
-      <c r="S48" t="e">
-        <v>#N/A</v>
+      <c r="S48" t="n">
+        <v>3</v>
       </c>
       <c r="T48" t="e">
         <v>#N/A</v>
@@ -7508,29 +7501,29 @@
       <c r="X48" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z48" t="e">
-        <v>#N/A</v>
+      <c r="Y48" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA48" t="s">
         <v>278</v>
       </c>
-      <c r="AB48" t="e">
-        <v>#N/A</v>
+      <c r="AB48" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC48" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF48" t="e">
-        <v>#N/A</v>
+      <c r="AD48" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG48" t="e">
         <v>#N/A</v>
@@ -7552,7 +7545,7 @@
       <c r="B49" t="s">
         <v>271</v>
       </c>
-      <c r="C49" s="34" t="s">
+      <c r="C49" t="s">
         <v>272</v>
       </c>
       <c r="D49" t="s">
@@ -7570,8 +7563,8 @@
       <c r="H49" t="n">
         <v>1.97</v>
       </c>
-      <c r="I49" t="e">
-        <v>#N/A</v>
+      <c r="I49" t="n">
+        <v>0.006</v>
       </c>
       <c r="J49" t="e">
         <v>#N/A</v>
@@ -7588,8 +7581,8 @@
       <c r="N49" t="n">
         <v>-23.6</v>
       </c>
-      <c r="O49" t="e">
-        <v>#N/A</v>
+      <c r="O49" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P49" t="e">
         <v>#N/A</v>
@@ -7600,8 +7593,8 @@
       <c r="R49" s="11" t="n">
         <v>28.3</v>
       </c>
-      <c r="S49" t="e">
-        <v>#N/A</v>
+      <c r="S49" t="n">
+        <v>3</v>
       </c>
       <c r="T49" t="e">
         <v>#N/A</v>
@@ -7618,29 +7611,29 @@
       <c r="X49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z49" t="e">
-        <v>#N/A</v>
+      <c r="Y49" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA49" t="s">
         <v>278</v>
       </c>
-      <c r="AB49" t="e">
-        <v>#N/A</v>
+      <c r="AB49" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF49" t="e">
-        <v>#N/A</v>
+      <c r="AD49" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG49" t="e">
         <v>#N/A</v>
@@ -7662,7 +7655,7 @@
       <c r="B50" t="s">
         <v>271</v>
       </c>
-      <c r="C50" s="34" t="s">
+      <c r="C50" t="s">
         <v>272</v>
       </c>
       <c r="D50" t="s">
@@ -7680,8 +7673,8 @@
       <c r="H50" t="n">
         <v>2</v>
       </c>
-      <c r="I50" t="e">
-        <v>#N/A</v>
+      <c r="I50" t="n">
+        <v>0.006</v>
       </c>
       <c r="J50" t="e">
         <v>#N/A</v>
@@ -7698,8 +7691,8 @@
       <c r="N50" t="n">
         <v>-23.2</v>
       </c>
-      <c r="O50" t="e">
-        <v>#N/A</v>
+      <c r="O50" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P50" t="e">
         <v>#N/A</v>
@@ -7710,8 +7703,8 @@
       <c r="R50" s="11" t="n">
         <v>27.2</v>
       </c>
-      <c r="S50" t="e">
-        <v>#N/A</v>
+      <c r="S50" t="n">
+        <v>3</v>
       </c>
       <c r="T50" t="e">
         <v>#N/A</v>
@@ -7728,29 +7721,29 @@
       <c r="X50" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z50" t="e">
-        <v>#N/A</v>
+      <c r="Y50" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA50" t="s">
         <v>278</v>
       </c>
-      <c r="AB50" t="e">
-        <v>#N/A</v>
+      <c r="AB50" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC50" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF50" t="e">
-        <v>#N/A</v>
+      <c r="AD50" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG50" t="e">
         <v>#N/A</v>
@@ -7772,7 +7765,7 @@
       <c r="B51" t="s">
         <v>271</v>
       </c>
-      <c r="C51" s="34" t="s">
+      <c r="C51" t="s">
         <v>272</v>
       </c>
       <c r="D51" t="s">
@@ -7790,8 +7783,8 @@
       <c r="H51" t="n">
         <v>2.07</v>
       </c>
-      <c r="I51" t="e">
-        <v>#N/A</v>
+      <c r="I51" t="n">
+        <v>0.006</v>
       </c>
       <c r="J51" t="e">
         <v>#N/A</v>
@@ -7808,8 +7801,8 @@
       <c r="N51" t="n">
         <v>-23.4</v>
       </c>
-      <c r="O51" t="e">
-        <v>#N/A</v>
+      <c r="O51" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P51" t="e">
         <v>#N/A</v>
@@ -7820,8 +7813,8 @@
       <c r="R51" s="11" t="n">
         <v>28.9</v>
       </c>
-      <c r="S51" t="e">
-        <v>#N/A</v>
+      <c r="S51" t="n">
+        <v>3</v>
       </c>
       <c r="T51" t="e">
         <v>#N/A</v>
@@ -7838,29 +7831,29 @@
       <c r="X51" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z51" t="e">
-        <v>#N/A</v>
+      <c r="Y51" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA51" t="s">
         <v>278</v>
       </c>
-      <c r="AB51" t="e">
-        <v>#N/A</v>
+      <c r="AB51" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC51" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF51" t="e">
-        <v>#N/A</v>
+      <c r="AD51" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG51" t="e">
         <v>#N/A</v>
@@ -7882,7 +7875,7 @@
       <c r="B52" t="s">
         <v>271</v>
       </c>
-      <c r="C52" s="34" t="s">
+      <c r="C52" t="s">
         <v>272</v>
       </c>
       <c r="D52" t="s">
@@ -7900,8 +7893,8 @@
       <c r="H52" t="n">
         <v>2.21</v>
       </c>
-      <c r="I52" t="e">
-        <v>#N/A</v>
+      <c r="I52" t="n">
+        <v>0.006</v>
       </c>
       <c r="J52" t="e">
         <v>#N/A</v>
@@ -7918,8 +7911,8 @@
       <c r="N52" t="n">
         <v>-23.8</v>
       </c>
-      <c r="O52" t="e">
-        <v>#N/A</v>
+      <c r="O52" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P52" t="e">
         <v>#N/A</v>
@@ -7930,8 +7923,8 @@
       <c r="R52" s="11" t="n">
         <v>28.5</v>
       </c>
-      <c r="S52" t="e">
-        <v>#N/A</v>
+      <c r="S52" t="n">
+        <v>3</v>
       </c>
       <c r="T52" t="e">
         <v>#N/A</v>
@@ -7948,29 +7941,29 @@
       <c r="X52" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z52" t="e">
-        <v>#N/A</v>
+      <c r="Y52" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA52" t="s">
         <v>278</v>
       </c>
-      <c r="AB52" t="e">
-        <v>#N/A</v>
+      <c r="AB52" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC52" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF52" t="e">
-        <v>#N/A</v>
+      <c r="AD52" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG52" t="e">
         <v>#N/A</v>
@@ -7992,7 +7985,7 @@
       <c r="B53" t="s">
         <v>271</v>
       </c>
-      <c r="C53" s="34" t="s">
+      <c r="C53" t="s">
         <v>272</v>
       </c>
       <c r="D53" t="s">
@@ -8010,8 +8003,8 @@
       <c r="H53" t="n">
         <v>2.3</v>
       </c>
-      <c r="I53" t="e">
-        <v>#N/A</v>
+      <c r="I53" t="n">
+        <v>0.006</v>
       </c>
       <c r="J53" t="e">
         <v>#N/A</v>
@@ -8028,8 +8021,8 @@
       <c r="N53" t="n">
         <v>-23.1</v>
       </c>
-      <c r="O53" t="e">
-        <v>#N/A</v>
+      <c r="O53" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P53" t="e">
         <v>#N/A</v>
@@ -8040,8 +8033,8 @@
       <c r="R53" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="S53" t="e">
-        <v>#N/A</v>
+      <c r="S53" t="n">
+        <v>3</v>
       </c>
       <c r="T53" t="e">
         <v>#N/A</v>
@@ -8058,29 +8051,29 @@
       <c r="X53" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z53" t="e">
-        <v>#N/A</v>
+      <c r="Y53" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA53" t="s">
         <v>278</v>
       </c>
-      <c r="AB53" t="e">
-        <v>#N/A</v>
+      <c r="AB53" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC53" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF53" t="e">
-        <v>#N/A</v>
+      <c r="AD53" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG53" t="e">
         <v>#N/A</v>
@@ -8102,7 +8095,7 @@
       <c r="B54" t="s">
         <v>271</v>
       </c>
-      <c r="C54" s="34" t="s">
+      <c r="C54" t="s">
         <v>272</v>
       </c>
       <c r="D54" t="s">
@@ -8120,8 +8113,8 @@
       <c r="H54" t="n">
         <v>2.49</v>
       </c>
-      <c r="I54" t="e">
-        <v>#N/A</v>
+      <c r="I54" t="n">
+        <v>0.006</v>
       </c>
       <c r="J54" t="e">
         <v>#N/A</v>
@@ -8138,8 +8131,8 @@
       <c r="N54" t="n">
         <v>-23.6</v>
       </c>
-      <c r="O54" t="e">
-        <v>#N/A</v>
+      <c r="O54" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P54" t="e">
         <v>#N/A</v>
@@ -8150,8 +8143,8 @@
       <c r="R54" s="11" t="n">
         <v>28.8</v>
       </c>
-      <c r="S54" t="e">
-        <v>#N/A</v>
+      <c r="S54" t="n">
+        <v>3</v>
       </c>
       <c r="T54" t="e">
         <v>#N/A</v>
@@ -8168,29 +8161,29 @@
       <c r="X54" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z54" t="e">
-        <v>#N/A</v>
+      <c r="Y54" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA54" t="s">
         <v>278</v>
       </c>
-      <c r="AB54" t="e">
-        <v>#N/A</v>
+      <c r="AB54" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC54" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF54" t="e">
-        <v>#N/A</v>
+      <c r="AD54" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG54" t="e">
         <v>#N/A</v>
@@ -8212,7 +8205,7 @@
       <c r="B55" t="s">
         <v>271</v>
       </c>
-      <c r="C55" s="34" t="s">
+      <c r="C55" t="s">
         <v>272</v>
       </c>
       <c r="D55" t="s">
@@ -8230,8 +8223,8 @@
       <c r="H55" t="n">
         <v>2.62</v>
       </c>
-      <c r="I55" t="e">
-        <v>#N/A</v>
+      <c r="I55" t="n">
+        <v>0.006</v>
       </c>
       <c r="J55" t="e">
         <v>#N/A</v>
@@ -8248,8 +8241,8 @@
       <c r="N55" t="n">
         <v>-23.7</v>
       </c>
-      <c r="O55" t="e">
-        <v>#N/A</v>
+      <c r="O55" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P55" t="e">
         <v>#N/A</v>
@@ -8260,8 +8253,8 @@
       <c r="R55" s="11" t="n">
         <v>28.1</v>
       </c>
-      <c r="S55" t="e">
-        <v>#N/A</v>
+      <c r="S55" t="n">
+        <v>3</v>
       </c>
       <c r="T55" t="e">
         <v>#N/A</v>
@@ -8278,29 +8271,29 @@
       <c r="X55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z55" t="e">
-        <v>#N/A</v>
+      <c r="Y55" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA55" t="s">
         <v>278</v>
       </c>
-      <c r="AB55" t="e">
-        <v>#N/A</v>
+      <c r="AB55" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF55" t="e">
-        <v>#N/A</v>
+      <c r="AD55" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG55" t="e">
         <v>#N/A</v>
@@ -8322,7 +8315,7 @@
       <c r="B56" t="s">
         <v>271</v>
       </c>
-      <c r="C56" s="34" t="s">
+      <c r="C56" t="s">
         <v>272</v>
       </c>
       <c r="D56" t="s">
@@ -8340,8 +8333,8 @@
       <c r="H56" t="n">
         <v>2.68</v>
       </c>
-      <c r="I56" t="e">
-        <v>#N/A</v>
+      <c r="I56" t="n">
+        <v>0.006</v>
       </c>
       <c r="J56" t="e">
         <v>#N/A</v>
@@ -8358,8 +8351,8 @@
       <c r="N56" t="n">
         <v>-23.5</v>
       </c>
-      <c r="O56" t="e">
-        <v>#N/A</v>
+      <c r="O56" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P56" t="e">
         <v>#N/A</v>
@@ -8370,8 +8363,8 @@
       <c r="R56" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="S56" t="e">
-        <v>#N/A</v>
+      <c r="S56" t="n">
+        <v>3</v>
       </c>
       <c r="T56" t="e">
         <v>#N/A</v>
@@ -8388,29 +8381,29 @@
       <c r="X56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z56" t="e">
-        <v>#N/A</v>
+      <c r="Y56" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA56" t="s">
         <v>278</v>
       </c>
-      <c r="AB56" t="e">
-        <v>#N/A</v>
+      <c r="AB56" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF56" t="e">
-        <v>#N/A</v>
+      <c r="AD56" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG56" t="e">
         <v>#N/A</v>
@@ -8432,7 +8425,7 @@
       <c r="B57" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="34" t="s">
+      <c r="C57" t="s">
         <v>272</v>
       </c>
       <c r="D57" t="s">
@@ -8450,8 +8443,8 @@
       <c r="H57" t="n">
         <v>2.81</v>
       </c>
-      <c r="I57" t="e">
-        <v>#N/A</v>
+      <c r="I57" t="n">
+        <v>0.006</v>
       </c>
       <c r="J57" t="e">
         <v>#N/A</v>
@@ -8468,8 +8461,8 @@
       <c r="N57" t="n">
         <v>-23.6</v>
       </c>
-      <c r="O57" t="e">
-        <v>#N/A</v>
+      <c r="O57" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P57" t="e">
         <v>#N/A</v>
@@ -8480,8 +8473,8 @@
       <c r="R57" s="11" t="n">
         <v>29.1</v>
       </c>
-      <c r="S57" t="e">
-        <v>#N/A</v>
+      <c r="S57" t="n">
+        <v>3</v>
       </c>
       <c r="T57" t="e">
         <v>#N/A</v>
@@ -8498,29 +8491,29 @@
       <c r="X57" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z57" t="e">
-        <v>#N/A</v>
+      <c r="Y57" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA57" t="s">
         <v>278</v>
       </c>
-      <c r="AB57" t="e">
-        <v>#N/A</v>
+      <c r="AB57" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC57" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF57" t="e">
-        <v>#N/A</v>
+      <c r="AD57" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG57" t="e">
         <v>#N/A</v>
@@ -8542,7 +8535,7 @@
       <c r="B58" t="s">
         <v>271</v>
       </c>
-      <c r="C58" s="34" t="s">
+      <c r="C58" t="s">
         <v>272</v>
       </c>
       <c r="D58" t="s">
@@ -8560,8 +8553,8 @@
       <c r="H58" t="n">
         <v>3.02</v>
       </c>
-      <c r="I58" t="e">
-        <v>#N/A</v>
+      <c r="I58" t="n">
+        <v>0.015</v>
       </c>
       <c r="J58" t="e">
         <v>#N/A</v>
@@ -8578,8 +8571,8 @@
       <c r="N58" t="n">
         <v>-24</v>
       </c>
-      <c r="O58" t="e">
-        <v>#N/A</v>
+      <c r="O58" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P58" t="e">
         <v>#N/A</v>
@@ -8590,8 +8583,8 @@
       <c r="R58" s="11" t="n">
         <v>28.8</v>
       </c>
-      <c r="S58" t="e">
-        <v>#N/A</v>
+      <c r="S58" t="n">
+        <v>3</v>
       </c>
       <c r="T58" t="e">
         <v>#N/A</v>
@@ -8608,29 +8601,29 @@
       <c r="X58" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z58" t="e">
-        <v>#N/A</v>
+      <c r="Y58" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA58" t="s">
         <v>278</v>
       </c>
-      <c r="AB58" t="e">
-        <v>#N/A</v>
+      <c r="AB58" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC58" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF58" t="e">
-        <v>#N/A</v>
+      <c r="AD58" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG58" t="e">
         <v>#N/A</v>
@@ -8652,7 +8645,7 @@
       <c r="B59" t="s">
         <v>271</v>
       </c>
-      <c r="C59" s="34" t="s">
+      <c r="C59" t="s">
         <v>272</v>
       </c>
       <c r="D59" t="s">
@@ -8670,8 +8663,8 @@
       <c r="H59" t="n">
         <v>3.16</v>
       </c>
-      <c r="I59" t="e">
-        <v>#N/A</v>
+      <c r="I59" t="n">
+        <v>0.015</v>
       </c>
       <c r="J59" t="e">
         <v>#N/A</v>
@@ -8688,8 +8681,8 @@
       <c r="N59" t="n">
         <v>-24.1</v>
       </c>
-      <c r="O59" t="e">
-        <v>#N/A</v>
+      <c r="O59" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P59" t="e">
         <v>#N/A</v>
@@ -8700,8 +8693,8 @@
       <c r="R59" s="11" t="n">
         <v>28.8</v>
       </c>
-      <c r="S59" t="e">
-        <v>#N/A</v>
+      <c r="S59" t="n">
+        <v>3</v>
       </c>
       <c r="T59" t="e">
         <v>#N/A</v>
@@ -8718,29 +8711,29 @@
       <c r="X59" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z59" t="e">
-        <v>#N/A</v>
+      <c r="Y59" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA59" t="s">
         <v>278</v>
       </c>
-      <c r="AB59" t="e">
-        <v>#N/A</v>
+      <c r="AB59" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC59" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF59" t="e">
-        <v>#N/A</v>
+      <c r="AD59" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG59" t="e">
         <v>#N/A</v>
@@ -8762,7 +8755,7 @@
       <c r="B60" t="s">
         <v>271</v>
       </c>
-      <c r="C60" s="34" t="s">
+      <c r="C60" t="s">
         <v>272</v>
       </c>
       <c r="D60" t="s">
@@ -8780,8 +8773,8 @@
       <c r="H60" t="n">
         <v>3.25</v>
       </c>
-      <c r="I60" t="e">
-        <v>#N/A</v>
+      <c r="I60" t="n">
+        <v>0.015</v>
       </c>
       <c r="J60" t="e">
         <v>#N/A</v>
@@ -8798,8 +8791,8 @@
       <c r="N60" t="n">
         <v>-24.2</v>
       </c>
-      <c r="O60" t="e">
-        <v>#N/A</v>
+      <c r="O60" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P60" t="e">
         <v>#N/A</v>
@@ -8810,8 +8803,8 @@
       <c r="R60" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="S60" t="e">
-        <v>#N/A</v>
+      <c r="S60" t="n">
+        <v>3</v>
       </c>
       <c r="T60" t="e">
         <v>#N/A</v>
@@ -8828,29 +8821,29 @@
       <c r="X60" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z60" t="e">
-        <v>#N/A</v>
+      <c r="Y60" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA60" t="s">
         <v>278</v>
       </c>
-      <c r="AB60" t="e">
-        <v>#N/A</v>
+      <c r="AB60" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC60" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF60" t="e">
-        <v>#N/A</v>
+      <c r="AD60" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG60" t="e">
         <v>#N/A</v>
@@ -8872,7 +8865,7 @@
       <c r="B61" t="s">
         <v>271</v>
       </c>
-      <c r="C61" s="34" t="s">
+      <c r="C61" t="s">
         <v>272</v>
       </c>
       <c r="D61" t="s">
@@ -8890,8 +8883,8 @@
       <c r="H61" t="n">
         <v>3.38</v>
       </c>
-      <c r="I61" t="e">
-        <v>#N/A</v>
+      <c r="I61" t="n">
+        <v>0.015</v>
       </c>
       <c r="J61" t="e">
         <v>#N/A</v>
@@ -8908,8 +8901,8 @@
       <c r="N61" t="n">
         <v>-23.9</v>
       </c>
-      <c r="O61" t="e">
-        <v>#N/A</v>
+      <c r="O61" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P61" t="e">
         <v>#N/A</v>
@@ -8920,8 +8913,8 @@
       <c r="R61" s="11" t="n">
         <v>28.2</v>
       </c>
-      <c r="S61" t="e">
-        <v>#N/A</v>
+      <c r="S61" t="n">
+        <v>3</v>
       </c>
       <c r="T61" t="e">
         <v>#N/A</v>
@@ -8938,29 +8931,29 @@
       <c r="X61" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z61" t="e">
-        <v>#N/A</v>
+      <c r="Y61" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA61" t="s">
         <v>278</v>
       </c>
-      <c r="AB61" t="e">
-        <v>#N/A</v>
+      <c r="AB61" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC61" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF61" t="e">
-        <v>#N/A</v>
+      <c r="AD61" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG61" t="e">
         <v>#N/A</v>
@@ -8982,7 +8975,7 @@
       <c r="B62" t="s">
         <v>271</v>
       </c>
-      <c r="C62" s="34" t="s">
+      <c r="C62" t="s">
         <v>272</v>
       </c>
       <c r="D62" t="s">
@@ -9000,8 +8993,8 @@
       <c r="H62" t="n">
         <v>3.46</v>
       </c>
-      <c r="I62" t="e">
-        <v>#N/A</v>
+      <c r="I62" t="n">
+        <v>0.015</v>
       </c>
       <c r="J62" t="e">
         <v>#N/A</v>
@@ -9018,8 +9011,8 @@
       <c r="N62" t="n">
         <v>-23.5</v>
       </c>
-      <c r="O62" t="e">
-        <v>#N/A</v>
+      <c r="O62" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P62" t="e">
         <v>#N/A</v>
@@ -9030,8 +9023,8 @@
       <c r="R62" s="11" t="n">
         <v>28.1</v>
       </c>
-      <c r="S62" t="e">
-        <v>#N/A</v>
+      <c r="S62" t="n">
+        <v>3</v>
       </c>
       <c r="T62" t="e">
         <v>#N/A</v>
@@ -9048,29 +9041,29 @@
       <c r="X62" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z62" t="e">
-        <v>#N/A</v>
+      <c r="Y62" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA62" t="s">
         <v>278</v>
       </c>
-      <c r="AB62" t="e">
-        <v>#N/A</v>
+      <c r="AB62" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC62" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF62" t="e">
-        <v>#N/A</v>
+      <c r="AD62" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG62" t="e">
         <v>#N/A</v>
@@ -9092,7 +9085,7 @@
       <c r="B63" t="s">
         <v>271</v>
       </c>
-      <c r="C63" s="34" t="s">
+      <c r="C63" t="s">
         <v>272</v>
       </c>
       <c r="D63" t="s">
@@ -9110,8 +9103,8 @@
       <c r="H63" t="n">
         <v>3.54</v>
       </c>
-      <c r="I63" t="e">
-        <v>#N/A</v>
+      <c r="I63" t="n">
+        <v>0.015</v>
       </c>
       <c r="J63" t="e">
         <v>#N/A</v>
@@ -9128,8 +9121,8 @@
       <c r="N63" t="n">
         <v>-23.6</v>
       </c>
-      <c r="O63" t="e">
-        <v>#N/A</v>
+      <c r="O63" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P63" t="e">
         <v>#N/A</v>
@@ -9140,8 +9133,8 @@
       <c r="R63" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="S63" t="e">
-        <v>#N/A</v>
+      <c r="S63" t="n">
+        <v>3</v>
       </c>
       <c r="T63" t="e">
         <v>#N/A</v>
@@ -9158,29 +9151,29 @@
       <c r="X63" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z63" t="e">
-        <v>#N/A</v>
+      <c r="Y63" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA63" t="s">
         <v>278</v>
       </c>
-      <c r="AB63" t="e">
-        <v>#N/A</v>
+      <c r="AB63" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC63" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF63" t="e">
-        <v>#N/A</v>
+      <c r="AD63" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG63" t="e">
         <v>#N/A</v>
@@ -9202,7 +9195,7 @@
       <c r="B64" t="s">
         <v>271</v>
       </c>
-      <c r="C64" s="34" t="s">
+      <c r="C64" t="s">
         <v>272</v>
       </c>
       <c r="D64" t="s">
@@ -9220,8 +9213,8 @@
       <c r="H64" t="n">
         <v>3.69</v>
       </c>
-      <c r="I64" t="e">
-        <v>#N/A</v>
+      <c r="I64" t="n">
+        <v>0.015</v>
       </c>
       <c r="J64" t="e">
         <v>#N/A</v>
@@ -9238,8 +9231,8 @@
       <c r="N64" t="n">
         <v>-23.7</v>
       </c>
-      <c r="O64" t="e">
-        <v>#N/A</v>
+      <c r="O64" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P64" t="e">
         <v>#N/A</v>
@@ -9250,8 +9243,8 @@
       <c r="R64" s="11" t="n">
         <v>29.4</v>
       </c>
-      <c r="S64" t="e">
-        <v>#N/A</v>
+      <c r="S64" t="n">
+        <v>3</v>
       </c>
       <c r="T64" t="e">
         <v>#N/A</v>
@@ -9268,29 +9261,29 @@
       <c r="X64" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z64" t="e">
-        <v>#N/A</v>
+      <c r="Y64" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA64" t="s">
         <v>278</v>
       </c>
-      <c r="AB64" t="e">
-        <v>#N/A</v>
+      <c r="AB64" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC64" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF64" t="e">
-        <v>#N/A</v>
+      <c r="AD64" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG64" t="e">
         <v>#N/A</v>
@@ -9312,7 +9305,7 @@
       <c r="B65" t="s">
         <v>271</v>
       </c>
-      <c r="C65" s="34" t="s">
+      <c r="C65" t="s">
         <v>272</v>
       </c>
       <c r="D65" t="s">
@@ -9330,8 +9323,8 @@
       <c r="H65" t="n">
         <v>3.81</v>
       </c>
-      <c r="I65" t="e">
-        <v>#N/A</v>
+      <c r="I65" t="n">
+        <v>0.015</v>
       </c>
       <c r="J65" t="e">
         <v>#N/A</v>
@@ -9348,8 +9341,8 @@
       <c r="N65" t="n">
         <v>-24.1</v>
       </c>
-      <c r="O65" t="e">
-        <v>#N/A</v>
+      <c r="O65" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P65" t="e">
         <v>#N/A</v>
@@ -9360,8 +9353,8 @@
       <c r="R65" s="11" t="n">
         <v>29.3</v>
       </c>
-      <c r="S65" t="e">
-        <v>#N/A</v>
+      <c r="S65" t="n">
+        <v>3</v>
       </c>
       <c r="T65" t="e">
         <v>#N/A</v>
@@ -9378,29 +9371,29 @@
       <c r="X65" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z65" t="e">
-        <v>#N/A</v>
+      <c r="Y65" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA65" t="s">
         <v>278</v>
       </c>
-      <c r="AB65" t="e">
-        <v>#N/A</v>
+      <c r="AB65" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC65" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF65" t="e">
-        <v>#N/A</v>
+      <c r="AD65" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG65" t="e">
         <v>#N/A</v>
@@ -9422,7 +9415,7 @@
       <c r="B66" t="s">
         <v>271</v>
       </c>
-      <c r="C66" s="34" t="s">
+      <c r="C66" t="s">
         <v>272</v>
       </c>
       <c r="D66" t="s">
@@ -9440,8 +9433,8 @@
       <c r="H66" t="n">
         <v>3.9</v>
       </c>
-      <c r="I66" t="e">
-        <v>#N/A</v>
+      <c r="I66" t="n">
+        <v>0.015</v>
       </c>
       <c r="J66" t="e">
         <v>#N/A</v>
@@ -9458,8 +9451,8 @@
       <c r="N66" t="n">
         <v>-24.1</v>
       </c>
-      <c r="O66" t="e">
-        <v>#N/A</v>
+      <c r="O66" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P66" t="e">
         <v>#N/A</v>
@@ -9470,8 +9463,8 @@
       <c r="R66" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="S66" t="e">
-        <v>#N/A</v>
+      <c r="S66" t="n">
+        <v>3</v>
       </c>
       <c r="T66" t="e">
         <v>#N/A</v>
@@ -9488,29 +9481,29 @@
       <c r="X66" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z66" t="e">
-        <v>#N/A</v>
+      <c r="Y66" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA66" t="s">
         <v>278</v>
       </c>
-      <c r="AB66" t="e">
-        <v>#N/A</v>
+      <c r="AB66" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC66" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF66" t="e">
-        <v>#N/A</v>
+      <c r="AD66" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG66" t="e">
         <v>#N/A</v>
@@ -9532,7 +9525,7 @@
       <c r="B67" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="34" t="s">
+      <c r="C67" t="s">
         <v>272</v>
       </c>
       <c r="D67" t="s">
@@ -9550,8 +9543,8 @@
       <c r="H67" t="n">
         <v>4</v>
       </c>
-      <c r="I67" t="e">
-        <v>#N/A</v>
+      <c r="I67" t="n">
+        <v>0.03</v>
       </c>
       <c r="J67" t="e">
         <v>#N/A</v>
@@ -9568,8 +9561,8 @@
       <c r="N67" t="n">
         <v>-23.8</v>
       </c>
-      <c r="O67" t="e">
-        <v>#N/A</v>
+      <c r="O67" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P67" t="e">
         <v>#N/A</v>
@@ -9580,8 +9573,8 @@
       <c r="R67" s="11" t="n">
         <v>28.7</v>
       </c>
-      <c r="S67" t="e">
-        <v>#N/A</v>
+      <c r="S67" t="n">
+        <v>3</v>
       </c>
       <c r="T67" t="e">
         <v>#N/A</v>
@@ -9598,29 +9591,29 @@
       <c r="X67" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z67" t="e">
-        <v>#N/A</v>
+      <c r="Y67" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA67" t="s">
         <v>278</v>
       </c>
-      <c r="AB67" t="e">
-        <v>#N/A</v>
+      <c r="AB67" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC67" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF67" t="e">
-        <v>#N/A</v>
+      <c r="AD67" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG67" t="e">
         <v>#N/A</v>
@@ -9642,7 +9635,7 @@
       <c r="B68" t="s">
         <v>271</v>
       </c>
-      <c r="C68" s="34" t="s">
+      <c r="C68" t="s">
         <v>272</v>
       </c>
       <c r="D68" t="s">
@@ -9660,8 +9653,8 @@
       <c r="H68" t="n">
         <v>4.11</v>
       </c>
-      <c r="I68" t="e">
-        <v>#N/A</v>
+      <c r="I68" t="n">
+        <v>0.03</v>
       </c>
       <c r="J68" t="e">
         <v>#N/A</v>
@@ -9678,8 +9671,8 @@
       <c r="N68" t="n">
         <v>-24</v>
       </c>
-      <c r="O68" t="e">
-        <v>#N/A</v>
+      <c r="O68" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P68" t="e">
         <v>#N/A</v>
@@ -9690,8 +9683,8 @@
       <c r="R68" s="11" t="n">
         <v>29.4</v>
       </c>
-      <c r="S68" t="e">
-        <v>#N/A</v>
+      <c r="S68" t="n">
+        <v>3</v>
       </c>
       <c r="T68" t="e">
         <v>#N/A</v>
@@ -9708,29 +9701,29 @@
       <c r="X68" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z68" t="e">
-        <v>#N/A</v>
+      <c r="Y68" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA68" t="s">
         <v>278</v>
       </c>
-      <c r="AB68" t="e">
-        <v>#N/A</v>
+      <c r="AB68" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC68" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF68" t="e">
-        <v>#N/A</v>
+      <c r="AD68" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG68" t="e">
         <v>#N/A</v>
@@ -9752,7 +9745,7 @@
       <c r="B69" t="s">
         <v>271</v>
       </c>
-      <c r="C69" s="34" t="s">
+      <c r="C69" t="s">
         <v>272</v>
       </c>
       <c r="D69" t="s">
@@ -9770,8 +9763,8 @@
       <c r="H69" t="n">
         <v>4.21</v>
       </c>
-      <c r="I69" t="e">
-        <v>#N/A</v>
+      <c r="I69" t="n">
+        <v>0.03</v>
       </c>
       <c r="J69" t="e">
         <v>#N/A</v>
@@ -9788,8 +9781,8 @@
       <c r="N69" t="n">
         <v>-24.5</v>
       </c>
-      <c r="O69" t="e">
-        <v>#N/A</v>
+      <c r="O69" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P69" t="e">
         <v>#N/A</v>
@@ -9800,8 +9793,8 @@
       <c r="R69" s="11" t="n">
         <v>28.9</v>
       </c>
-      <c r="S69" t="e">
-        <v>#N/A</v>
+      <c r="S69" t="n">
+        <v>3</v>
       </c>
       <c r="T69" t="e">
         <v>#N/A</v>
@@ -9818,29 +9811,29 @@
       <c r="X69" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z69" t="e">
-        <v>#N/A</v>
+      <c r="Y69" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA69" t="s">
         <v>278</v>
       </c>
-      <c r="AB69" t="e">
-        <v>#N/A</v>
+      <c r="AB69" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC69" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF69" t="e">
-        <v>#N/A</v>
+      <c r="AD69" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG69" t="e">
         <v>#N/A</v>
@@ -9862,7 +9855,7 @@
       <c r="B70" t="s">
         <v>271</v>
       </c>
-      <c r="C70" s="34" t="s">
+      <c r="C70" t="s">
         <v>272</v>
       </c>
       <c r="D70" t="s">
@@ -9880,8 +9873,8 @@
       <c r="H70" t="n">
         <v>4.3</v>
       </c>
-      <c r="I70" t="e">
-        <v>#N/A</v>
+      <c r="I70" t="n">
+        <v>0.03</v>
       </c>
       <c r="J70" t="e">
         <v>#N/A</v>
@@ -9898,8 +9891,8 @@
       <c r="N70" t="n">
         <v>-24.3</v>
       </c>
-      <c r="O70" t="e">
-        <v>#N/A</v>
+      <c r="O70" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P70" t="e">
         <v>#N/A</v>
@@ -9910,8 +9903,8 @@
       <c r="R70" s="11" t="n">
         <v>29.6</v>
       </c>
-      <c r="S70" t="e">
-        <v>#N/A</v>
+      <c r="S70" t="n">
+        <v>3</v>
       </c>
       <c r="T70" t="e">
         <v>#N/A</v>
@@ -9928,29 +9921,29 @@
       <c r="X70" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z70" t="e">
-        <v>#N/A</v>
+      <c r="Y70" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA70" t="s">
         <v>278</v>
       </c>
-      <c r="AB70" t="e">
-        <v>#N/A</v>
+      <c r="AB70" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC70" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF70" t="e">
-        <v>#N/A</v>
+      <c r="AD70" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG70" t="e">
         <v>#N/A</v>
@@ -9972,7 +9965,7 @@
       <c r="B71" t="s">
         <v>271</v>
       </c>
-      <c r="C71" s="34" t="s">
+      <c r="C71" t="s">
         <v>272</v>
       </c>
       <c r="D71" t="s">
@@ -9990,8 +9983,8 @@
       <c r="H71" t="n">
         <v>4.39</v>
       </c>
-      <c r="I71" t="e">
-        <v>#N/A</v>
+      <c r="I71" t="n">
+        <v>0.03</v>
       </c>
       <c r="J71" t="e">
         <v>#N/A</v>
@@ -10008,8 +10001,8 @@
       <c r="N71" t="n">
         <v>-23.7</v>
       </c>
-      <c r="O71" t="e">
-        <v>#N/A</v>
+      <c r="O71" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P71" t="e">
         <v>#N/A</v>
@@ -10020,8 +10013,8 @@
       <c r="R71" s="11" t="n">
         <v>28.7</v>
       </c>
-      <c r="S71" t="e">
-        <v>#N/A</v>
+      <c r="S71" t="n">
+        <v>3</v>
       </c>
       <c r="T71" t="e">
         <v>#N/A</v>
@@ -10038,29 +10031,29 @@
       <c r="X71" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z71" t="e">
-        <v>#N/A</v>
+      <c r="Y71" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA71" t="s">
         <v>278</v>
       </c>
-      <c r="AB71" t="e">
-        <v>#N/A</v>
+      <c r="AB71" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC71" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF71" t="e">
-        <v>#N/A</v>
+      <c r="AD71" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG71" t="e">
         <v>#N/A</v>
@@ -10082,7 +10075,7 @@
       <c r="B72" t="s">
         <v>271</v>
       </c>
-      <c r="C72" s="34" t="s">
+      <c r="C72" t="s">
         <v>272</v>
       </c>
       <c r="D72" t="s">
@@ -10100,8 +10093,8 @@
       <c r="H72" t="n">
         <v>4.54</v>
       </c>
-      <c r="I72" t="e">
-        <v>#N/A</v>
+      <c r="I72" t="n">
+        <v>0.03</v>
       </c>
       <c r="J72" t="e">
         <v>#N/A</v>
@@ -10118,8 +10111,8 @@
       <c r="N72" t="n">
         <v>-24.2</v>
       </c>
-      <c r="O72" t="e">
-        <v>#N/A</v>
+      <c r="O72" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P72" t="e">
         <v>#N/A</v>
@@ -10130,8 +10123,8 @@
       <c r="R72" s="11" t="n">
         <v>29.1</v>
       </c>
-      <c r="S72" t="e">
-        <v>#N/A</v>
+      <c r="S72" t="n">
+        <v>3</v>
       </c>
       <c r="T72" t="e">
         <v>#N/A</v>
@@ -10148,29 +10141,29 @@
       <c r="X72" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z72" t="e">
-        <v>#N/A</v>
+      <c r="Y72" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA72" t="s">
         <v>278</v>
       </c>
-      <c r="AB72" t="e">
-        <v>#N/A</v>
+      <c r="AB72" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC72" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF72" t="e">
-        <v>#N/A</v>
+      <c r="AD72" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG72" t="e">
         <v>#N/A</v>
@@ -10192,7 +10185,7 @@
       <c r="B73" t="s">
         <v>271</v>
       </c>
-      <c r="C73" s="34" t="s">
+      <c r="C73" t="s">
         <v>272</v>
       </c>
       <c r="D73" t="s">
@@ -10210,8 +10203,8 @@
       <c r="H73" t="n">
         <v>4.58</v>
       </c>
-      <c r="I73" t="e">
-        <v>#N/A</v>
+      <c r="I73" t="n">
+        <v>0.03</v>
       </c>
       <c r="J73" t="e">
         <v>#N/A</v>
@@ -10228,8 +10221,8 @@
       <c r="N73" t="n">
         <v>-24.1</v>
       </c>
-      <c r="O73" t="e">
-        <v>#N/A</v>
+      <c r="O73" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P73" t="e">
         <v>#N/A</v>
@@ -10240,8 +10233,8 @@
       <c r="R73" s="11" t="n">
         <v>29.3</v>
       </c>
-      <c r="S73" t="e">
-        <v>#N/A</v>
+      <c r="S73" t="n">
+        <v>3</v>
       </c>
       <c r="T73" t="e">
         <v>#N/A</v>
@@ -10258,29 +10251,29 @@
       <c r="X73" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z73" t="e">
-        <v>#N/A</v>
+      <c r="Y73" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA73" t="s">
         <v>278</v>
       </c>
-      <c r="AB73" t="e">
-        <v>#N/A</v>
+      <c r="AB73" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC73" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF73" t="e">
-        <v>#N/A</v>
+      <c r="AD73" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG73" t="e">
         <v>#N/A</v>
@@ -10302,7 +10295,7 @@
       <c r="B74" t="s">
         <v>271</v>
       </c>
-      <c r="C74" s="34" t="s">
+      <c r="C74" t="s">
         <v>272</v>
       </c>
       <c r="D74" t="s">
@@ -10320,8 +10313,8 @@
       <c r="H74" t="n">
         <v>4.62</v>
       </c>
-      <c r="I74" t="e">
-        <v>#N/A</v>
+      <c r="I74" t="n">
+        <v>0.03</v>
       </c>
       <c r="J74" t="e">
         <v>#N/A</v>
@@ -10338,8 +10331,8 @@
       <c r="N74" t="n">
         <v>-24.4</v>
       </c>
-      <c r="O74" t="e">
-        <v>#N/A</v>
+      <c r="O74" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P74" t="e">
         <v>#N/A</v>
@@ -10350,8 +10343,8 @@
       <c r="R74" s="11" t="n">
         <v>28.7</v>
       </c>
-      <c r="S74" t="e">
-        <v>#N/A</v>
+      <c r="S74" t="n">
+        <v>3</v>
       </c>
       <c r="T74" t="e">
         <v>#N/A</v>
@@ -10368,29 +10361,29 @@
       <c r="X74" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z74" t="e">
-        <v>#N/A</v>
+      <c r="Y74" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA74" t="s">
         <v>278</v>
       </c>
-      <c r="AB74" t="e">
-        <v>#N/A</v>
+      <c r="AB74" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC74" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF74" t="e">
-        <v>#N/A</v>
+      <c r="AD74" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG74" t="e">
         <v>#N/A</v>
@@ -10412,7 +10405,7 @@
       <c r="B75" t="s">
         <v>271</v>
       </c>
-      <c r="C75" s="34" t="s">
+      <c r="C75" t="s">
         <v>272</v>
       </c>
       <c r="D75" t="s">
@@ -10430,8 +10423,8 @@
       <c r="H75" t="n">
         <v>4.69</v>
       </c>
-      <c r="I75" t="e">
-        <v>#N/A</v>
+      <c r="I75" t="n">
+        <v>0.03</v>
       </c>
       <c r="J75" t="e">
         <v>#N/A</v>
@@ -10448,8 +10441,8 @@
       <c r="N75" t="n">
         <v>-24.1</v>
       </c>
-      <c r="O75" t="e">
-        <v>#N/A</v>
+      <c r="O75" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P75" t="e">
         <v>#N/A</v>
@@ -10460,8 +10453,8 @@
       <c r="R75" s="11" t="n">
         <v>28.8</v>
       </c>
-      <c r="S75" t="e">
-        <v>#N/A</v>
+      <c r="S75" t="n">
+        <v>3</v>
       </c>
       <c r="T75" t="e">
         <v>#N/A</v>
@@ -10478,29 +10471,29 @@
       <c r="X75" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z75" t="e">
-        <v>#N/A</v>
+      <c r="Y75" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.54</v>
       </c>
       <c r="AA75" t="s">
         <v>278</v>
       </c>
-      <c r="AB75" t="e">
-        <v>#N/A</v>
+      <c r="AB75" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC75" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF75" t="e">
-        <v>#N/A</v>
+      <c r="AD75" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG75" t="e">
         <v>#N/A</v>
@@ -10645,79 +10638,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-    <hyperlink ref="C37" r:id="rId33h"/>
-    <hyperlink ref="C38" r:id="rId34h"/>
-    <hyperlink ref="C39" r:id="rId35h"/>
-    <hyperlink ref="C40" r:id="rId36h"/>
-    <hyperlink ref="C41" r:id="rId37h"/>
-    <hyperlink ref="C42" r:id="rId38h"/>
-    <hyperlink ref="C43" r:id="rId39h"/>
-    <hyperlink ref="C44" r:id="rId40h"/>
-    <hyperlink ref="C45" r:id="rId41h"/>
-    <hyperlink ref="C46" r:id="rId42h"/>
-    <hyperlink ref="C47" r:id="rId43h"/>
-    <hyperlink ref="C48" r:id="rId44h"/>
-    <hyperlink ref="C49" r:id="rId45h"/>
-    <hyperlink ref="C50" r:id="rId46h"/>
-    <hyperlink ref="C51" r:id="rId47h"/>
-    <hyperlink ref="C52" r:id="rId48h"/>
-    <hyperlink ref="C53" r:id="rId49h"/>
-    <hyperlink ref="C54" r:id="rId50h"/>
-    <hyperlink ref="C55" r:id="rId51h"/>
-    <hyperlink ref="C56" r:id="rId52h"/>
-    <hyperlink ref="C57" r:id="rId53h"/>
-    <hyperlink ref="C58" r:id="rId54h"/>
-    <hyperlink ref="C59" r:id="rId55h"/>
-    <hyperlink ref="C60" r:id="rId56h"/>
-    <hyperlink ref="C61" r:id="rId57h"/>
-    <hyperlink ref="C62" r:id="rId58h"/>
-    <hyperlink ref="C63" r:id="rId59h"/>
-    <hyperlink ref="C64" r:id="rId60h"/>
-    <hyperlink ref="C65" r:id="rId61h"/>
-    <hyperlink ref="C66" r:id="rId62h"/>
-    <hyperlink ref="C67" r:id="rId63h"/>
-    <hyperlink ref="C68" r:id="rId64h"/>
-    <hyperlink ref="C69" r:id="rId65h"/>
-    <hyperlink ref="C70" r:id="rId66h"/>
-    <hyperlink ref="C71" r:id="rId67h"/>
-    <hyperlink ref="C72" r:id="rId68h"/>
-    <hyperlink ref="C73" r:id="rId69h"/>
-    <hyperlink ref="C74" r:id="rId70h"/>
-    <hyperlink ref="C75" r:id="rId71h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
